--- a/research/traditional_assets/database/data/morocco/morocco_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_shipbuilding_marine.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1117432886994339</v>
+        <v>0.1114163101755957</v>
       </c>
       <c r="C2">
-        <v>4048.748538019734</v>
+        <v>4027.873542227805</v>
       </c>
       <c r="D2">
-        <v>3999.848538019734</v>
+        <v>4019.780542227805</v>
       </c>
       <c r="E2">
-        <v>-198.6</v>
+        <v>-157.793</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>40.807</v>
       </c>
       <c r="G2">
         <v>48.9</v>
@@ -1451,28 +1451,28 @@
         <v>186.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.0525921</v>
       </c>
       <c r="N2">
-        <v>186.6</v>
+        <v>184.5474079</v>
       </c>
       <c r="O2">
-        <v>59.712</v>
+        <v>59.055170528</v>
       </c>
       <c r="P2">
-        <v>126.888</v>
+        <v>125.492237372</v>
       </c>
       <c r="Q2">
-        <v>173.088</v>
+        <v>171.692237372</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1117432886994339</v>
+        <v>0.1121962325006017</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8653654896701227</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>90.90944079927034</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1114163101755957</v>
+        <v>0.1110893316517575</v>
       </c>
       <c r="C3">
-        <v>4027.873542227805</v>
+        <v>4007.198191221575</v>
       </c>
       <c r="D3">
-        <v>4019.780542227805</v>
+        <v>4039.912191221575</v>
       </c>
       <c r="E3">
-        <v>-157.793</v>
+        <v>-116.986</v>
       </c>
       <c r="F3">
-        <v>40.807</v>
+        <v>81.614</v>
       </c>
       <c r="G3">
         <v>48.9</v>
@@ -1533,28 +1533,28 @@
         <v>186.6</v>
       </c>
       <c r="M3">
-        <v>2.0525921</v>
+        <v>4.1051842</v>
       </c>
       <c r="N3">
-        <v>184.5474079</v>
+        <v>182.4948158</v>
       </c>
       <c r="O3">
-        <v>59.055170528</v>
+        <v>58.398341056</v>
       </c>
       <c r="P3">
-        <v>125.492237372</v>
+        <v>124.096474744</v>
       </c>
       <c r="Q3">
-        <v>171.692237372</v>
+        <v>170.296474744</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1121962325006017</v>
+        <v>0.1126584200528138</v>
       </c>
       <c r="T3">
-        <v>0.8653654896701227</v>
+        <v>0.871389342867453</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>90.90944079927034</v>
+        <v>45.45472039963517</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1110893316517575</v>
+        <v>0.1107623531279193</v>
       </c>
       <c r="C4">
-        <v>4007.198191221575</v>
+        <v>3986.725499649727</v>
       </c>
       <c r="D4">
-        <v>4039.912191221575</v>
+        <v>4060.246499649727</v>
       </c>
       <c r="E4">
-        <v>-116.986</v>
+        <v>-76.179</v>
       </c>
       <c r="F4">
-        <v>81.614</v>
+        <v>122.421</v>
       </c>
       <c r="G4">
         <v>48.9</v>
@@ -1615,28 +1615,28 @@
         <v>186.6</v>
       </c>
       <c r="M4">
-        <v>4.1051842</v>
+        <v>6.157776299999999</v>
       </c>
       <c r="N4">
-        <v>182.4948158</v>
+        <v>180.4422237</v>
       </c>
       <c r="O4">
-        <v>58.398341056</v>
+        <v>57.741511584</v>
       </c>
       <c r="P4">
-        <v>124.096474744</v>
+        <v>122.700712116</v>
       </c>
       <c r="Q4">
-        <v>170.296474744</v>
+        <v>168.900712116</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1126584200528138</v>
+        <v>0.1131301372452777</v>
       </c>
       <c r="T4">
-        <v>0.871389342867453</v>
+        <v>0.8775373992234912</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>45.45472039963517</v>
+        <v>30.30314693309012</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1107623531279193</v>
+        <v>0.1104353746040811</v>
       </c>
       <c r="C5">
-        <v>3986.725499649727</v>
+        <v>3966.458543163158</v>
       </c>
       <c r="D5">
-        <v>4060.246499649727</v>
+        <v>4080.786543163158</v>
       </c>
       <c r="E5">
-        <v>-76.179</v>
+        <v>-35.37199999999999</v>
       </c>
       <c r="F5">
-        <v>122.421</v>
+        <v>163.228</v>
       </c>
       <c r="G5">
         <v>48.9</v>
@@ -1697,28 +1697,28 @@
         <v>186.6</v>
       </c>
       <c r="M5">
-        <v>6.157776299999999</v>
+        <v>8.2103684</v>
       </c>
       <c r="N5">
-        <v>180.4422237</v>
+        <v>178.3896316</v>
       </c>
       <c r="O5">
-        <v>57.741511584</v>
+        <v>57.084682112</v>
       </c>
       <c r="P5">
-        <v>122.700712116</v>
+        <v>121.304949488</v>
       </c>
       <c r="Q5">
-        <v>168.900712116</v>
+        <v>167.504949488</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1131301372452777</v>
+        <v>0.1136116818792512</v>
       </c>
       <c r="T5">
-        <v>0.8775373992234912</v>
+        <v>0.8838135400869467</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>30.30314693309012</v>
+        <v>22.72736019981759</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1104353746040811</v>
+        <v>0.1101083960802429</v>
       </c>
       <c r="C6">
-        <v>3966.458543163158</v>
+        <v>3946.400459965828</v>
       </c>
       <c r="D6">
-        <v>4080.786543163158</v>
+        <v>4101.535459965829</v>
       </c>
       <c r="E6">
-        <v>-35.37199999999999</v>
+        <v>5.435000000000002</v>
       </c>
       <c r="F6">
-        <v>163.228</v>
+        <v>204.035</v>
       </c>
       <c r="G6">
         <v>48.9</v>
@@ -1779,28 +1779,28 @@
         <v>186.6</v>
       </c>
       <c r="M6">
-        <v>8.2103684</v>
+        <v>10.2629605</v>
       </c>
       <c r="N6">
-        <v>178.3896316</v>
+        <v>176.3370395</v>
       </c>
       <c r="O6">
-        <v>57.084682112</v>
+        <v>56.42785264</v>
       </c>
       <c r="P6">
-        <v>121.304949488</v>
+        <v>119.90918686</v>
       </c>
       <c r="Q6">
-        <v>167.504949488</v>
+        <v>166.10918686</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1136116818792512</v>
+        <v>0.1141033642949926</v>
       </c>
       <c r="T6">
-        <v>0.8838135400869467</v>
+        <v>0.8902218102317382</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>22.72736019981759</v>
+        <v>18.18188815985407</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1101083960802429</v>
+        <v>0.1097814175564047</v>
       </c>
       <c r="C7">
-        <v>3946.400459965828</v>
+        <v>3926.554452413164</v>
       </c>
       <c r="D7">
-        <v>4101.535459965829</v>
+        <v>4122.496452413165</v>
       </c>
       <c r="E7">
-        <v>5.435000000000002</v>
+        <v>46.24200000000002</v>
       </c>
       <c r="F7">
-        <v>204.035</v>
+        <v>244.842</v>
       </c>
       <c r="G7">
         <v>48.9</v>
@@ -1861,28 +1861,28 @@
         <v>186.6</v>
       </c>
       <c r="M7">
-        <v>10.2629605</v>
+        <v>12.3155526</v>
       </c>
       <c r="N7">
-        <v>176.3370395</v>
+        <v>174.2844474</v>
       </c>
       <c r="O7">
-        <v>56.42785264</v>
+        <v>55.771023168</v>
       </c>
       <c r="P7">
-        <v>119.90918686</v>
+        <v>118.513424232</v>
       </c>
       <c r="Q7">
-        <v>166.10918686</v>
+        <v>164.713424232</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1141033642949926</v>
+        <v>0.1146055080387285</v>
       </c>
       <c r="T7">
-        <v>0.8902218102317382</v>
+        <v>0.8967664265498231</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.18188815985407</v>
+        <v>15.15157346654506</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1097814175564047</v>
+        <v>0.1094544390325666</v>
       </c>
       <c r="C8">
-        <v>3926.554452413164</v>
+        <v>3906.9237886597</v>
       </c>
       <c r="D8">
-        <v>4122.496452413165</v>
+        <v>4143.6727886597</v>
       </c>
       <c r="E8">
-        <v>46.24199999999999</v>
+        <v>87.04899999999995</v>
       </c>
       <c r="F8">
-        <v>244.842</v>
+        <v>285.6489999999999</v>
       </c>
       <c r="G8">
         <v>48.9</v>
@@ -1943,28 +1943,28 @@
         <v>186.6</v>
       </c>
       <c r="M8">
-        <v>12.3155526</v>
+        <v>14.3681447</v>
       </c>
       <c r="N8">
-        <v>174.2844474</v>
+        <v>172.2318553</v>
       </c>
       <c r="O8">
-        <v>55.771023168</v>
+        <v>55.114193696</v>
       </c>
       <c r="P8">
-        <v>118.513424232</v>
+        <v>117.117661604</v>
       </c>
       <c r="Q8">
-        <v>164.713424232</v>
+        <v>163.317661604</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1146055080387285</v>
+        <v>0.1151184505726522</v>
       </c>
       <c r="T8">
-        <v>0.8967664265498231</v>
+        <v>0.9034517873048561</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.15157346654506</v>
+        <v>12.98706297132434</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1094544390325665</v>
+        <v>0.1092090605087284</v>
       </c>
       <c r="C9">
-        <v>3906.923788659701</v>
+        <v>3882.151852166274</v>
       </c>
       <c r="D9">
-        <v>4143.672788659701</v>
+        <v>4159.707852166274</v>
       </c>
       <c r="E9">
-        <v>87.04900000000001</v>
+        <v>127.856</v>
       </c>
       <c r="F9">
-        <v>285.649</v>
+        <v>326.456</v>
       </c>
       <c r="G9">
         <v>48.9</v>
@@ -2025,45 +2025,45 @@
         <v>186.6</v>
       </c>
       <c r="M9">
-        <v>14.3681447</v>
+        <v>16.9104208</v>
       </c>
       <c r="N9">
-        <v>172.2318553</v>
+        <v>169.6895792</v>
       </c>
       <c r="O9">
-        <v>55.114193696</v>
+        <v>54.300665344</v>
       </c>
       <c r="P9">
-        <v>117.117661604</v>
+        <v>115.388913856</v>
       </c>
       <c r="Q9">
-        <v>163.317661604</v>
+        <v>161.588913856</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1151184505726522</v>
+        <v>0.1156425440312265</v>
       </c>
       <c r="T9">
-        <v>0.9034517873048561</v>
+        <v>0.9102824819893462</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.32</v>
       </c>
       <c r="W9">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>12.98706297132434</v>
+        <v>11.03461600435159</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1092090605087284</v>
+        <v>0.1089963219848902</v>
       </c>
       <c r="C10">
-        <v>3882.151852166274</v>
+        <v>3855.347725755651</v>
       </c>
       <c r="D10">
-        <v>4159.707852166274</v>
+        <v>4173.710725755652</v>
       </c>
       <c r="E10">
-        <v>127.856</v>
+        <v>168.663</v>
       </c>
       <c r="F10">
-        <v>326.456</v>
+        <v>367.263</v>
       </c>
       <c r="G10">
         <v>48.9</v>
@@ -2107,45 +2107,45 @@
         <v>186.6</v>
       </c>
       <c r="M10">
-        <v>16.9104208</v>
+        <v>19.6485705</v>
       </c>
       <c r="N10">
-        <v>169.6895792</v>
+        <v>166.9514295</v>
       </c>
       <c r="O10">
-        <v>54.300665344</v>
+        <v>53.42445744</v>
       </c>
       <c r="P10">
-        <v>115.388913856</v>
+        <v>113.52697206</v>
       </c>
       <c r="Q10">
-        <v>161.588913856</v>
+        <v>159.72697206</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1156425440312265</v>
+        <v>0.1161781560273518</v>
       </c>
       <c r="T10">
-        <v>0.9102824819893462</v>
+        <v>0.9172633018317374</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>11.03461600435159</v>
+        <v>9.49687408557279</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1089963219848902</v>
+        <v>0.108691103461052</v>
       </c>
       <c r="C11">
-        <v>3855.347725755651</v>
+        <v>3834.796274736942</v>
       </c>
       <c r="D11">
-        <v>4173.710725755652</v>
+        <v>4193.966274736942</v>
       </c>
       <c r="E11">
-        <v>168.663</v>
+        <v>209.4699999999999</v>
       </c>
       <c r="F11">
-        <v>367.263</v>
+        <v>408.0699999999999</v>
       </c>
       <c r="G11">
         <v>48.9</v>
@@ -2189,28 +2189,28 @@
         <v>186.6</v>
       </c>
       <c r="M11">
-        <v>19.6485705</v>
+        <v>21.83174499999999</v>
       </c>
       <c r="N11">
-        <v>166.9514295</v>
+        <v>164.768255</v>
       </c>
       <c r="O11">
-        <v>53.42445744</v>
+        <v>52.7258416</v>
       </c>
       <c r="P11">
-        <v>113.52697206</v>
+        <v>112.0424134</v>
       </c>
       <c r="Q11">
-        <v>159.72697206</v>
+        <v>158.2424134</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1161781560273518</v>
+        <v>0.11672567051228</v>
       </c>
       <c r="T11">
-        <v>0.9172633018317374</v>
+        <v>0.9243992510039594</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.49687408557279</v>
+        <v>8.547186677015514</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.108691103461052</v>
+        <v>0.1083858849372138</v>
       </c>
       <c r="C12">
-        <v>3834.796274736942</v>
+        <v>3814.442388033759</v>
       </c>
       <c r="D12">
-        <v>4193.966274736942</v>
+        <v>4214.419388033759</v>
       </c>
       <c r="E12">
-        <v>209.47</v>
+        <v>250.277</v>
       </c>
       <c r="F12">
-        <v>408.07</v>
+        <v>448.877</v>
       </c>
       <c r="G12">
         <v>48.9</v>
@@ -2271,28 +2271,28 @@
         <v>186.6</v>
       </c>
       <c r="M12">
-        <v>21.831745</v>
+        <v>24.0149195</v>
       </c>
       <c r="N12">
-        <v>164.768255</v>
+        <v>162.5850805</v>
       </c>
       <c r="O12">
-        <v>52.7258416</v>
+        <v>52.02722576</v>
       </c>
       <c r="P12">
-        <v>112.0424134</v>
+        <v>110.55785474</v>
       </c>
       <c r="Q12">
-        <v>158.2424134</v>
+        <v>156.75785474</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.11672567051228</v>
+        <v>0.1172854886934987</v>
       </c>
       <c r="T12">
-        <v>0.9243992510039594</v>
+        <v>0.9316955585845459</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.547186677015512</v>
+        <v>7.770169706377737</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1083858849372138</v>
+        <v>0.1081459464133756</v>
       </c>
       <c r="C13">
-        <v>3814.442388033759</v>
+        <v>3789.854591125091</v>
       </c>
       <c r="D13">
-        <v>4214.419388033759</v>
+        <v>4230.638591125092</v>
       </c>
       <c r="E13">
-        <v>250.277</v>
+        <v>291.0839999999999</v>
       </c>
       <c r="F13">
-        <v>448.877</v>
+        <v>489.684</v>
       </c>
       <c r="G13">
         <v>48.9</v>
@@ -2353,45 +2353,45 @@
         <v>186.6</v>
       </c>
       <c r="M13">
-        <v>24.0149195</v>
+        <v>26.5898412</v>
       </c>
       <c r="N13">
-        <v>162.5850805</v>
+        <v>160.0101588</v>
       </c>
       <c r="O13">
-        <v>52.02722576</v>
+        <v>51.203250816</v>
       </c>
       <c r="P13">
-        <v>110.55785474</v>
+        <v>108.806907984</v>
       </c>
       <c r="Q13">
-        <v>156.75785474</v>
+        <v>155.006907984</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1172854886934987</v>
+        <v>0.1178580300151996</v>
       </c>
       <c r="T13">
-        <v>0.9316955585845459</v>
+        <v>0.9391576913374186</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.770169706377737</v>
+        <v>7.017717728979894</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1081459464133756</v>
+        <v>0.1078461678895374</v>
       </c>
       <c r="C14">
-        <v>3789.854591125091</v>
+        <v>3769.488089464945</v>
       </c>
       <c r="D14">
-        <v>4230.638591125092</v>
+        <v>4251.079089464945</v>
       </c>
       <c r="E14">
-        <v>291.0839999999999</v>
+        <v>331.891</v>
       </c>
       <c r="F14">
-        <v>489.684</v>
+        <v>530.491</v>
       </c>
       <c r="G14">
         <v>48.9</v>
@@ -2435,28 +2435,28 @@
         <v>186.6</v>
       </c>
       <c r="M14">
-        <v>26.5898412</v>
+        <v>28.8056613</v>
       </c>
       <c r="N14">
-        <v>160.0101588</v>
+        <v>157.7943387</v>
       </c>
       <c r="O14">
-        <v>51.203250816</v>
+        <v>50.494188384</v>
       </c>
       <c r="P14">
-        <v>108.806907984</v>
+        <v>107.300150316</v>
       </c>
       <c r="Q14">
-        <v>155.006907984</v>
+        <v>153.500150316</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1178580300151996</v>
+        <v>0.1184437332063649</v>
       </c>
       <c r="T14">
-        <v>0.9391576913374186</v>
+        <v>0.9467913673719663</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.017717728979894</v>
+        <v>6.477893288289132</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1078461678895374</v>
+        <v>0.1076415893656992</v>
       </c>
       <c r="C15">
-        <v>3769.488089464945</v>
+        <v>3742.744109089155</v>
       </c>
       <c r="D15">
-        <v>4251.079089464945</v>
+        <v>4265.142109089155</v>
       </c>
       <c r="E15">
-        <v>331.891</v>
+        <v>372.698</v>
       </c>
       <c r="F15">
-        <v>530.491</v>
+        <v>571.298</v>
       </c>
       <c r="G15">
         <v>48.9</v>
@@ -2517,45 +2517,45 @@
         <v>186.6</v>
       </c>
       <c r="M15">
-        <v>28.8056613</v>
+        <v>31.5927794</v>
       </c>
       <c r="N15">
-        <v>157.7943387</v>
+        <v>155.0072206</v>
       </c>
       <c r="O15">
-        <v>50.494188384</v>
+        <v>49.60231059199999</v>
       </c>
       <c r="P15">
-        <v>107.300150316</v>
+        <v>105.404910008</v>
       </c>
       <c r="Q15">
-        <v>153.500150316</v>
+        <v>151.604910008</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1184437332063649</v>
+        <v>0.1190430574019758</v>
       </c>
       <c r="T15">
-        <v>0.9467913673719663</v>
+        <v>0.9546025707561547</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.32</v>
       </c>
       <c r="W15">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.477893288289132</v>
+        <v>5.906412906488372</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1076415893656992</v>
+        <v>0.1073486108418611</v>
       </c>
       <c r="C16">
-        <v>3742.744109089155</v>
+        <v>3722.239680048744</v>
       </c>
       <c r="D16">
-        <v>4265.142109089155</v>
+        <v>4285.444680048744</v>
       </c>
       <c r="E16">
-        <v>372.698</v>
+        <v>413.505</v>
       </c>
       <c r="F16">
-        <v>571.298</v>
+        <v>612.105</v>
       </c>
       <c r="G16">
         <v>48.9</v>
@@ -2599,28 +2599,28 @@
         <v>186.6</v>
       </c>
       <c r="M16">
-        <v>31.5927794</v>
+        <v>33.8494065</v>
       </c>
       <c r="N16">
-        <v>155.0072206</v>
+        <v>152.7505935</v>
       </c>
       <c r="O16">
-        <v>49.60231059199999</v>
+        <v>48.88018991999999</v>
       </c>
       <c r="P16">
-        <v>105.404910008</v>
+        <v>103.87040358</v>
       </c>
       <c r="Q16">
-        <v>151.604910008</v>
+        <v>150.07040358</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1190430574019758</v>
+        <v>0.119656483343366</v>
       </c>
       <c r="T16">
-        <v>0.9546025707561547</v>
+        <v>0.9625975671611479</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.906412906488372</v>
+        <v>5.512652046055814</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1073486108418611</v>
+        <v>0.1070556323180229</v>
       </c>
       <c r="C17">
-        <v>3722.239680048744</v>
+        <v>3701.929460652239</v>
       </c>
       <c r="D17">
-        <v>4285.444680048744</v>
+        <v>4305.94146065224</v>
       </c>
       <c r="E17">
-        <v>413.5049999999999</v>
+        <v>454.312</v>
       </c>
       <c r="F17">
-        <v>612.1049999999999</v>
+        <v>652.912</v>
       </c>
       <c r="G17">
         <v>48.9</v>
@@ -2681,28 +2681,28 @@
         <v>186.6</v>
       </c>
       <c r="M17">
-        <v>33.84940649999999</v>
+        <v>36.1060336</v>
       </c>
       <c r="N17">
-        <v>152.7505935</v>
+        <v>150.4939664</v>
       </c>
       <c r="O17">
-        <v>48.88018992000001</v>
+        <v>48.158069248</v>
       </c>
       <c r="P17">
-        <v>103.87040358</v>
+        <v>102.335897152</v>
       </c>
       <c r="Q17">
-        <v>150.07040358</v>
+        <v>148.535897152</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.119656483343366</v>
+        <v>0.1202845146643129</v>
       </c>
       <c r="T17">
-        <v>0.9625975671611479</v>
+        <v>0.9707829206234024</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.512652046055816</v>
+        <v>5.168111293177326</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1070556323180229</v>
+        <v>0.1067626537941847</v>
       </c>
       <c r="C18">
-        <v>3701.929460652239</v>
+        <v>3681.816250937923</v>
       </c>
       <c r="D18">
-        <v>4305.94146065224</v>
+        <v>4326.635250937923</v>
       </c>
       <c r="E18">
-        <v>454.312</v>
+        <v>495.119</v>
       </c>
       <c r="F18">
-        <v>652.912</v>
+        <v>693.7190000000001</v>
       </c>
       <c r="G18">
         <v>48.9</v>
@@ -2763,28 +2763,28 @@
         <v>186.6</v>
       </c>
       <c r="M18">
-        <v>36.1060336</v>
+        <v>38.36266070000001</v>
       </c>
       <c r="N18">
-        <v>150.4939664</v>
+        <v>148.2373393</v>
       </c>
       <c r="O18">
-        <v>48.158069248</v>
+        <v>47.43594857599999</v>
       </c>
       <c r="P18">
-        <v>102.335897152</v>
+        <v>100.801390724</v>
       </c>
       <c r="Q18">
-        <v>148.535897152</v>
+        <v>147.001390724</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1202845146643129</v>
+        <v>0.120927679270102</v>
       </c>
       <c r="T18">
-        <v>0.9707829206234024</v>
+        <v>0.9791655115184825</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.168111293177326</v>
+        <v>4.864104746519835</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1067626537941847</v>
+        <v>0.1064696752703465</v>
       </c>
       <c r="C19">
-        <v>3681.816250937923</v>
+        <v>3661.902905030474</v>
       </c>
       <c r="D19">
-        <v>4326.635250937923</v>
+        <v>4347.528905030475</v>
       </c>
       <c r="E19">
-        <v>495.119</v>
+        <v>535.926</v>
       </c>
       <c r="F19">
-        <v>693.7190000000001</v>
+        <v>734.5260000000001</v>
       </c>
       <c r="G19">
         <v>48.9</v>
@@ -2845,28 +2845,28 @@
         <v>186.6</v>
       </c>
       <c r="M19">
-        <v>38.36266070000001</v>
+        <v>40.6192878</v>
       </c>
       <c r="N19">
-        <v>148.2373393</v>
+        <v>145.9807122</v>
       </c>
       <c r="O19">
-        <v>47.43594857599999</v>
+        <v>46.713827904</v>
       </c>
       <c r="P19">
-        <v>100.801390724</v>
+        <v>99.266884296</v>
       </c>
       <c r="Q19">
-        <v>147.001390724</v>
+        <v>145.466884296</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.120927679270102</v>
+        <v>0.1215865308174957</v>
       </c>
       <c r="T19">
-        <v>0.9791655115184825</v>
+        <v>0.9877525558500279</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.864104746519835</v>
+        <v>4.593876705046512</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1064696752703465</v>
+        <v>0.1064996967465083</v>
       </c>
       <c r="C20">
-        <v>3661.902905030473</v>
+        <v>3618.945659767631</v>
       </c>
       <c r="D20">
-        <v>4347.528905030474</v>
+        <v>4345.378659767632</v>
       </c>
       <c r="E20">
-        <v>535.9259999999999</v>
+        <v>576.7329999999999</v>
       </c>
       <c r="F20">
-        <v>734.526</v>
+        <v>775.333</v>
       </c>
       <c r="G20">
         <v>48.9</v>
@@ -2927,45 +2927,45 @@
         <v>186.6</v>
       </c>
       <c r="M20">
-        <v>40.6192878</v>
+        <v>44.8142474</v>
       </c>
       <c r="N20">
-        <v>145.9807122</v>
+        <v>141.7857526</v>
       </c>
       <c r="O20">
-        <v>46.713827904</v>
+        <v>45.371440832</v>
       </c>
       <c r="P20">
-        <v>99.266884296</v>
+        <v>96.414311768</v>
       </c>
       <c r="Q20">
-        <v>145.466884296</v>
+        <v>142.614311768</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1215865308174957</v>
+        <v>0.1222616503043312</v>
       </c>
       <c r="T20">
-        <v>0.9877525558500279</v>
+        <v>0.9965516259675374</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.32</v>
       </c>
       <c r="W20">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.593876705046512</v>
+        <v>4.163854372794844</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1064996967465083</v>
+        <v>0.1066997182226701</v>
       </c>
       <c r="C21">
-        <v>3618.945659767631</v>
+        <v>3563.86652387973</v>
       </c>
       <c r="D21">
-        <v>4345.378659767632</v>
+        <v>4331.10652387973</v>
       </c>
       <c r="E21">
-        <v>576.7329999999999</v>
+        <v>617.54</v>
       </c>
       <c r="F21">
-        <v>775.333</v>
+        <v>816.14</v>
       </c>
       <c r="G21">
         <v>48.9</v>
@@ -3009,45 +3009,45 @@
         <v>186.6</v>
       </c>
       <c r="M21">
-        <v>44.8142474</v>
+        <v>50.029382</v>
       </c>
       <c r="N21">
-        <v>141.7857526</v>
+        <v>136.570618</v>
       </c>
       <c r="O21">
-        <v>45.371440832</v>
+        <v>43.70259776</v>
       </c>
       <c r="P21">
-        <v>96.414311768</v>
+        <v>92.86802023999999</v>
       </c>
       <c r="Q21">
-        <v>142.614311768</v>
+        <v>139.06802024</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1222616503043312</v>
+        <v>0.1229536477783376</v>
       </c>
       <c r="T21">
-        <v>0.9965516259675374</v>
+        <v>1.005570672837985</v>
       </c>
       <c r="U21">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V21">
         <v>0.32</v>
       </c>
       <c r="W21">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.163854372794844</v>
+        <v>3.729808215500244</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1066997182226701</v>
+        <v>0.1064475396988319</v>
       </c>
       <c r="C22">
-        <v>3563.86652387973</v>
+        <v>3541.068697132295</v>
       </c>
       <c r="D22">
-        <v>4331.10652387973</v>
+        <v>4349.115697132295</v>
       </c>
       <c r="E22">
-        <v>617.54</v>
+        <v>658.347</v>
       </c>
       <c r="F22">
-        <v>816.14</v>
+        <v>856.947</v>
       </c>
       <c r="G22">
         <v>48.9</v>
@@ -3091,28 +3091,28 @@
         <v>186.6</v>
       </c>
       <c r="M22">
-        <v>50.029382</v>
+        <v>52.5308511</v>
       </c>
       <c r="N22">
-        <v>136.570618</v>
+        <v>134.0691489</v>
       </c>
       <c r="O22">
-        <v>43.70259776</v>
+        <v>42.902127648</v>
       </c>
       <c r="P22">
-        <v>92.86802023999999</v>
+        <v>91.16702125199998</v>
       </c>
       <c r="Q22">
-        <v>139.06802024</v>
+        <v>137.367021252</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1229536477783376</v>
+        <v>0.1236631641757366</v>
       </c>
       <c r="T22">
-        <v>1.005570672837985</v>
+        <v>1.01481805000895</v>
       </c>
       <c r="U22">
         <v>0.0613</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.729808215500244</v>
+        <v>3.552198300476422</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1064475396988319</v>
+        <v>0.1066142411749937</v>
       </c>
       <c r="C23">
-        <v>3541.068697132295</v>
+        <v>3488.340081525445</v>
       </c>
       <c r="D23">
-        <v>4349.115697132295</v>
+        <v>4337.194081525446</v>
       </c>
       <c r="E23">
-        <v>658.3469999999999</v>
+        <v>699.154</v>
       </c>
       <c r="F23">
-        <v>856.9469999999999</v>
+        <v>897.754</v>
       </c>
       <c r="G23">
         <v>48.9</v>
@@ -3173,45 +3173,45 @@
         <v>186.6</v>
       </c>
       <c r="M23">
-        <v>52.53085109999999</v>
+        <v>57.5460314</v>
       </c>
       <c r="N23">
-        <v>134.0691489</v>
+        <v>129.0539686</v>
       </c>
       <c r="O23">
-        <v>42.902127648</v>
+        <v>41.297269952</v>
       </c>
       <c r="P23">
-        <v>91.16702125200001</v>
+        <v>87.756698648</v>
       </c>
       <c r="Q23">
-        <v>137.367021252</v>
+        <v>133.956698648</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1236631641757366</v>
+        <v>0.124390873301274</v>
       </c>
       <c r="T23">
-        <v>1.01481805000895</v>
+        <v>1.024302539415068</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.32</v>
       </c>
       <c r="W23">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.552198300476423</v>
+        <v>3.242621523332363</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1066142411749937</v>
+        <v>0.1063811026511556</v>
       </c>
       <c r="C24">
-        <v>3488.340081525445</v>
+        <v>3464.224210962112</v>
       </c>
       <c r="D24">
-        <v>4337.194081525446</v>
+        <v>4353.885210962113</v>
       </c>
       <c r="E24">
-        <v>699.154</v>
+        <v>739.961</v>
       </c>
       <c r="F24">
-        <v>897.754</v>
+        <v>938.561</v>
       </c>
       <c r="G24">
         <v>48.9</v>
@@ -3255,28 +3255,28 @@
         <v>186.6</v>
       </c>
       <c r="M24">
-        <v>57.5460314</v>
+        <v>60.16176010000001</v>
       </c>
       <c r="N24">
-        <v>129.0539686</v>
+        <v>126.4382399</v>
       </c>
       <c r="O24">
-        <v>41.297269952</v>
+        <v>40.46023676799999</v>
       </c>
       <c r="P24">
-        <v>87.756698648</v>
+        <v>85.978003132</v>
       </c>
       <c r="Q24">
-        <v>133.956698648</v>
+        <v>132.178003132</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.124390873301274</v>
+        <v>0.1251374839625397</v>
       </c>
       <c r="T24">
-        <v>1.024302539415068</v>
+        <v>1.03403337919537</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.242621523332363</v>
+        <v>3.101637978839651</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1063811026511556</v>
+        <v>0.1074209241273174</v>
       </c>
       <c r="C25">
-        <v>3464.224210962112</v>
+        <v>3349.947632061484</v>
       </c>
       <c r="D25">
-        <v>4353.885210962113</v>
+        <v>4280.415632061485</v>
       </c>
       <c r="E25">
-        <v>739.961</v>
+        <v>780.768</v>
       </c>
       <c r="F25">
-        <v>938.561</v>
+        <v>979.3680000000001</v>
       </c>
       <c r="G25">
         <v>48.9</v>
@@ -3337,45 +3337,45 @@
         <v>186.6</v>
       </c>
       <c r="M25">
-        <v>60.16176010000001</v>
+        <v>70.41655920000001</v>
       </c>
       <c r="N25">
-        <v>126.4382399</v>
+        <v>116.1834408</v>
       </c>
       <c r="O25">
-        <v>40.46023676799999</v>
+        <v>37.17870105599999</v>
       </c>
       <c r="P25">
-        <v>85.978003132</v>
+        <v>79.00473974399999</v>
       </c>
       <c r="Q25">
-        <v>132.178003132</v>
+        <v>125.204739744</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1251374839625397</v>
+        <v>0.125903742272786</v>
       </c>
       <c r="T25">
-        <v>1.03403337919537</v>
+        <v>1.044020293706734</v>
       </c>
       <c r="U25">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V25">
         <v>0.32</v>
       </c>
       <c r="W25">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.101637978839651</v>
+        <v>2.649944872625926</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1074209241273174</v>
+        <v>0.1072408256034792</v>
       </c>
       <c r="C26">
-        <v>3349.947632061484</v>
+        <v>3321.687607613593</v>
       </c>
       <c r="D26">
-        <v>4280.415632061485</v>
+        <v>4292.962607613594</v>
       </c>
       <c r="E26">
-        <v>780.7679999999999</v>
+        <v>821.5749999999999</v>
       </c>
       <c r="F26">
-        <v>979.3679999999999</v>
+        <v>1020.175</v>
       </c>
       <c r="G26">
         <v>48.9</v>
@@ -3419,28 +3419,28 @@
         <v>186.6</v>
       </c>
       <c r="M26">
-        <v>70.41655919999999</v>
+        <v>73.3505825</v>
       </c>
       <c r="N26">
-        <v>116.1834408</v>
+        <v>113.2494175</v>
       </c>
       <c r="O26">
-        <v>37.178701056</v>
+        <v>36.2398136</v>
       </c>
       <c r="P26">
-        <v>79.00473974400001</v>
+        <v>77.0096039</v>
       </c>
       <c r="Q26">
-        <v>125.204739744</v>
+        <v>123.2096039</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.125903742272786</v>
+        <v>0.1266904341379722</v>
       </c>
       <c r="T26">
-        <v>1.044020293706734</v>
+        <v>1.0542735259384</v>
       </c>
       <c r="U26">
         <v>0.07190000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.649944872625927</v>
+        <v>2.543947077720889</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1072408256034792</v>
+        <v>0.107750247079641</v>
       </c>
       <c r="C27">
-        <v>3321.687607613593</v>
+        <v>3245.579257711523</v>
       </c>
       <c r="D27">
-        <v>4292.962607613594</v>
+        <v>4257.661257711524</v>
       </c>
       <c r="E27">
-        <v>821.5749999999999</v>
+        <v>862.3819999999999</v>
       </c>
       <c r="F27">
-        <v>1020.175</v>
+        <v>1060.982</v>
       </c>
       <c r="G27">
         <v>48.9</v>
@@ -3501,45 +3501,45 @@
         <v>186.6</v>
       </c>
       <c r="M27">
-        <v>73.3505825</v>
+        <v>80.4224356</v>
       </c>
       <c r="N27">
-        <v>113.2494175</v>
+        <v>106.1775644</v>
       </c>
       <c r="O27">
-        <v>36.2398136</v>
+        <v>33.976820608</v>
       </c>
       <c r="P27">
-        <v>77.0096039</v>
+        <v>72.200743792</v>
       </c>
       <c r="Q27">
-        <v>123.2096039</v>
+        <v>118.400743792</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1266904341379722</v>
+        <v>0.1274983879454608</v>
       </c>
       <c r="T27">
-        <v>1.0542735259384</v>
+        <v>1.064803872554706</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.32</v>
       </c>
       <c r="W27">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.543947077720889</v>
+        <v>2.320248057744722</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.107750247079641</v>
+        <v>0.1075966685558028</v>
       </c>
       <c r="C28">
-        <v>3245.579257711523</v>
+        <v>3215.353496898744</v>
       </c>
       <c r="D28">
-        <v>4257.661257711524</v>
+        <v>4268.242496898744</v>
       </c>
       <c r="E28">
-        <v>862.3819999999999</v>
+        <v>903.189</v>
       </c>
       <c r="F28">
-        <v>1060.982</v>
+        <v>1101.789</v>
       </c>
       <c r="G28">
         <v>48.9</v>
@@ -3583,28 +3583,28 @@
         <v>186.6</v>
       </c>
       <c r="M28">
-        <v>80.4224356</v>
+        <v>83.51560620000001</v>
       </c>
       <c r="N28">
-        <v>106.1775644</v>
+        <v>103.0843938</v>
       </c>
       <c r="O28">
-        <v>33.976820608</v>
+        <v>32.987006016</v>
       </c>
       <c r="P28">
-        <v>72.200743792</v>
+        <v>70.09738778399999</v>
       </c>
       <c r="Q28">
-        <v>118.400743792</v>
+        <v>116.297387784</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1274983879454608</v>
+        <v>0.1283284774737025</v>
       </c>
       <c r="T28">
-        <v>1.064803872554706</v>
+        <v>1.075622721818034</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.320248057744722</v>
+        <v>2.234312944494917</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1075966685558028</v>
+        <v>0.1074430900319646</v>
       </c>
       <c r="C29">
-        <v>3215.353496898744</v>
+        <v>3185.180460603634</v>
       </c>
       <c r="D29">
-        <v>4268.242496898744</v>
+        <v>4278.876460603635</v>
       </c>
       <c r="E29">
-        <v>903.189</v>
+        <v>943.996</v>
       </c>
       <c r="F29">
-        <v>1101.789</v>
+        <v>1142.596</v>
       </c>
       <c r="G29">
         <v>48.9</v>
@@ -3665,28 +3665,28 @@
         <v>186.6</v>
       </c>
       <c r="M29">
-        <v>83.51560620000001</v>
+        <v>86.6087768</v>
       </c>
       <c r="N29">
-        <v>103.0843938</v>
+        <v>99.99122319999999</v>
       </c>
       <c r="O29">
-        <v>32.987006016</v>
+        <v>31.997191424</v>
       </c>
       <c r="P29">
-        <v>70.09738778399999</v>
+        <v>67.994031776</v>
       </c>
       <c r="Q29">
-        <v>116.297387784</v>
+        <v>114.194031776</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1283284774737025</v>
+        <v>0.1291816250443953</v>
       </c>
       <c r="T29">
-        <v>1.075622721818034</v>
+        <v>1.08674209467201</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.234312944494917</v>
+        <v>2.154516053620099</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1074430900319646</v>
+        <v>0.1072895115081264</v>
       </c>
       <c r="C30">
-        <v>3185.180460603634</v>
+        <v>3155.060543886425</v>
       </c>
       <c r="D30">
-        <v>4278.876460603635</v>
+        <v>4289.563543886426</v>
       </c>
       <c r="E30">
-        <v>943.996</v>
+        <v>984.803</v>
       </c>
       <c r="F30">
-        <v>1142.596</v>
+        <v>1183.403</v>
       </c>
       <c r="G30">
         <v>48.9</v>
@@ -3747,28 +3747,28 @@
         <v>186.6</v>
       </c>
       <c r="M30">
-        <v>86.6087768</v>
+        <v>89.70194740000001</v>
       </c>
       <c r="N30">
-        <v>99.99122319999999</v>
+        <v>96.89805259999999</v>
       </c>
       <c r="O30">
-        <v>31.997191424</v>
+        <v>31.00737683199999</v>
       </c>
       <c r="P30">
-        <v>67.994031776</v>
+        <v>65.89067576799999</v>
       </c>
       <c r="Q30">
-        <v>114.194031776</v>
+        <v>112.090675768</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1291816250443953</v>
+        <v>0.1300588049410231</v>
       </c>
       <c r="T30">
-        <v>1.08674209467201</v>
+        <v>1.098174689296521</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.154516053620099</v>
+        <v>2.080222396598716</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1072895115081264</v>
+        <v>0.1071359329842882</v>
       </c>
       <c r="C31">
-        <v>3155.060543886425</v>
+        <v>3124.994145764104</v>
       </c>
       <c r="D31">
-        <v>4289.563543886426</v>
+        <v>4300.304145764105</v>
       </c>
       <c r="E31">
-        <v>984.8029999999998</v>
+        <v>1025.61</v>
       </c>
       <c r="F31">
-        <v>1183.403</v>
+        <v>1224.21</v>
       </c>
       <c r="G31">
         <v>48.9</v>
@@ -3829,28 +3829,28 @@
         <v>186.6</v>
       </c>
       <c r="M31">
-        <v>89.70194739999999</v>
+        <v>92.79511799999999</v>
       </c>
       <c r="N31">
-        <v>96.8980526</v>
+        <v>93.80488200000001</v>
       </c>
       <c r="O31">
-        <v>31.007376832</v>
+        <v>30.01756224</v>
       </c>
       <c r="P31">
-        <v>65.89067576799999</v>
+        <v>63.78731976</v>
       </c>
       <c r="Q31">
-        <v>112.090675768</v>
+        <v>109.98731976</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1300588049410231</v>
+        <v>0.1309610471204118</v>
       </c>
       <c r="T31">
-        <v>1.098174689296521</v>
+        <v>1.109933929481732</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.080222396598717</v>
+        <v>2.010881650045426</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1071359329842882</v>
+        <v>0.10997571446045</v>
       </c>
       <c r="C32">
-        <v>3124.994145764104</v>
+        <v>2893.89827780723</v>
       </c>
       <c r="D32">
-        <v>4300.304145764105</v>
+        <v>4110.01527780723</v>
       </c>
       <c r="E32">
-        <v>1025.61</v>
+        <v>1066.417</v>
       </c>
       <c r="F32">
-        <v>1224.21</v>
+        <v>1265.017</v>
       </c>
       <c r="G32">
         <v>48.9</v>
@@ -3911,45 +3911,45 @@
         <v>186.6</v>
       </c>
       <c r="M32">
-        <v>92.79511799999999</v>
+        <v>113.85153</v>
       </c>
       <c r="N32">
-        <v>93.80488200000001</v>
+        <v>72.74847000000001</v>
       </c>
       <c r="O32">
-        <v>30.01756224</v>
+        <v>23.2795104</v>
       </c>
       <c r="P32">
-        <v>63.78731976</v>
+        <v>49.46895960000001</v>
       </c>
       <c r="Q32">
-        <v>109.98731976</v>
+        <v>95.66895960000002</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1309610471204118</v>
+        <v>0.131889441247029</v>
       </c>
       <c r="T32">
-        <v>1.109933929481732</v>
+        <v>1.122034017208543</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.010881650045426</v>
+        <v>1.638976656703691</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.10997571446045</v>
+        <v>0.1099186959366119</v>
       </c>
       <c r="C33">
-        <v>2893.89827780723</v>
+        <v>2856.746171292968</v>
       </c>
       <c r="D33">
-        <v>4110.01527780723</v>
+        <v>4113.670171292969</v>
       </c>
       <c r="E33">
-        <v>1066.417</v>
+        <v>1107.224</v>
       </c>
       <c r="F33">
-        <v>1265.017</v>
+        <v>1305.824</v>
       </c>
       <c r="G33">
         <v>48.9</v>
@@ -3993,28 +3993,28 @@
         <v>186.6</v>
       </c>
       <c r="M33">
-        <v>113.85153</v>
+        <v>117.52416</v>
       </c>
       <c r="N33">
-        <v>72.74847000000001</v>
+        <v>69.07584</v>
       </c>
       <c r="O33">
-        <v>23.2795104</v>
+        <v>22.1042688</v>
       </c>
       <c r="P33">
-        <v>49.46895960000001</v>
+        <v>46.9715712</v>
       </c>
       <c r="Q33">
-        <v>95.66895960000002</v>
+        <v>93.17157120000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.131889441247029</v>
+        <v>0.1328451410832527</v>
       </c>
       <c r="T33">
-        <v>1.122034017208543</v>
+        <v>1.134489989868496</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.638976656703691</v>
+        <v>1.587758636181701</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1099186959366119</v>
+        <v>0.1098616774127736</v>
       </c>
       <c r="C34">
-        <v>2856.746171292968</v>
+        <v>2819.600570903426</v>
       </c>
       <c r="D34">
-        <v>4113.670171292969</v>
+        <v>4117.331570903427</v>
       </c>
       <c r="E34">
-        <v>1107.224</v>
+        <v>1148.031</v>
       </c>
       <c r="F34">
-        <v>1305.824</v>
+        <v>1346.631</v>
       </c>
       <c r="G34">
         <v>48.9</v>
@@ -4075,28 +4075,28 @@
         <v>186.6</v>
       </c>
       <c r="M34">
-        <v>117.52416</v>
+        <v>121.19679</v>
       </c>
       <c r="N34">
-        <v>69.07584</v>
+        <v>65.40320999999999</v>
       </c>
       <c r="O34">
-        <v>22.1042688</v>
+        <v>20.9290272</v>
       </c>
       <c r="P34">
-        <v>46.9715712</v>
+        <v>44.47418279999999</v>
       </c>
       <c r="Q34">
-        <v>93.17157120000002</v>
+        <v>90.67418280000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1328451410832527</v>
+        <v>0.1338293692727965</v>
       </c>
       <c r="T34">
-        <v>1.134489989868496</v>
+        <v>1.14731778260785</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.587758636181701</v>
+        <v>1.539644738115589</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1098616774127736</v>
+        <v>0.1248773860837172</v>
       </c>
       <c r="C35">
-        <v>2819.600570903426</v>
+        <v>1996.968899752662</v>
       </c>
       <c r="D35">
-        <v>4117.331570903427</v>
+        <v>3335.506899752662</v>
       </c>
       <c r="E35">
-        <v>1148.031</v>
+        <v>1188.838</v>
       </c>
       <c r="F35">
-        <v>1346.631</v>
+        <v>1387.438</v>
       </c>
       <c r="G35">
         <v>48.9</v>
@@ -4157,45 +4157,45 @@
         <v>186.6</v>
       </c>
       <c r="M35">
-        <v>121.19679</v>
+        <v>203.6758984</v>
       </c>
       <c r="N35">
-        <v>65.40320999999999</v>
+        <v>-17.07589840000003</v>
       </c>
       <c r="O35">
-        <v>20.9290272</v>
+        <v>-5.464287488000009</v>
       </c>
       <c r="P35">
-        <v>44.47418279999999</v>
+        <v>-11.61161091200002</v>
       </c>
       <c r="Q35">
-        <v>90.67418280000001</v>
+        <v>34.588389088</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1338293692727965</v>
+        <v>0.1357548025375269</v>
       </c>
       <c r="T35">
-        <v>1.14731778260785</v>
+        <v>1.172412632680035</v>
       </c>
       <c r="U35">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.32</v>
+        <v>0.2931716539319313</v>
       </c>
       <c r="W35">
-        <v>0.06119999999999999</v>
+        <v>0.1037624012027925</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.539644738115589</v>
+        <v>0.9161614185372852</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1248773860837172</v>
+        <v>0.1258873860837172</v>
       </c>
       <c r="C36">
-        <v>1996.968899752662</v>
+        <v>1914.097073648478</v>
       </c>
       <c r="D36">
-        <v>3335.506899752662</v>
+        <v>3293.442073648478</v>
       </c>
       <c r="E36">
-        <v>1188.838</v>
+        <v>1229.645</v>
       </c>
       <c r="F36">
-        <v>1387.438</v>
+        <v>1428.245</v>
       </c>
       <c r="G36">
         <v>48.9</v>
@@ -4239,37 +4239,37 @@
         <v>186.6</v>
       </c>
       <c r="M36">
-        <v>203.6758984</v>
+        <v>209.666366</v>
       </c>
       <c r="N36">
-        <v>-17.07589840000003</v>
+        <v>-23.06636600000004</v>
       </c>
       <c r="O36">
-        <v>-5.464287488000009</v>
+        <v>-7.381237120000015</v>
       </c>
       <c r="P36">
-        <v>-11.61161091200002</v>
+        <v>-15.68512888000003</v>
       </c>
       <c r="Q36">
-        <v>34.588389088</v>
+        <v>30.51487111999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1357548025375269</v>
+        <v>0.1371387225765658</v>
       </c>
       <c r="T36">
-        <v>1.172412632680035</v>
+        <v>1.190449750105882</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2931716539319313</v>
+        <v>0.2847953209624475</v>
       </c>
       <c r="W36">
-        <v>0.1037624012027925</v>
+        <v>0.1049920468827127</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.9161614185372852</v>
+        <v>0.8899853780076484</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1258873860837172</v>
+        <v>0.1268973860837172</v>
       </c>
       <c r="C37">
-        <v>1914.097073648478</v>
+        <v>1832.273011878434</v>
       </c>
       <c r="D37">
-        <v>3293.442073648478</v>
+        <v>3252.425011878434</v>
       </c>
       <c r="E37">
-        <v>1229.645</v>
+        <v>1270.452</v>
       </c>
       <c r="F37">
-        <v>1428.245</v>
+        <v>1469.052</v>
       </c>
       <c r="G37">
         <v>48.9</v>
@@ -4321,37 +4321,37 @@
         <v>186.6</v>
       </c>
       <c r="M37">
-        <v>209.666366</v>
+        <v>215.6568336</v>
       </c>
       <c r="N37">
-        <v>-23.06636600000004</v>
+        <v>-29.05683360000003</v>
       </c>
       <c r="O37">
-        <v>-7.381237120000015</v>
+        <v>-9.29818675200001</v>
       </c>
       <c r="P37">
-        <v>-15.68512888000003</v>
+        <v>-19.75864684800002</v>
       </c>
       <c r="Q37">
-        <v>30.51487111999999</v>
+        <v>26.44135315199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1371387225765658</v>
+        <v>0.1385658901168246</v>
       </c>
       <c r="T37">
-        <v>1.190449750105882</v>
+        <v>1.209050527451287</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2847953209624475</v>
+        <v>0.2768843398246018</v>
       </c>
       <c r="W37">
-        <v>0.1049920468827127</v>
+        <v>0.1061533789137485</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8899853780076484</v>
+        <v>0.8652635619518805</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1268973860837172</v>
+        <v>0.1279073860837172</v>
       </c>
       <c r="C38">
-        <v>1832.273011878435</v>
+        <v>1751.458048908477</v>
       </c>
       <c r="D38">
-        <v>3252.425011878434</v>
+        <v>3212.417048908477</v>
       </c>
       <c r="E38">
-        <v>1270.452</v>
+        <v>1311.259</v>
       </c>
       <c r="F38">
-        <v>1469.052</v>
+        <v>1509.859</v>
       </c>
       <c r="G38">
         <v>48.9</v>
@@ -4403,37 +4403,37 @@
         <v>186.6</v>
       </c>
       <c r="M38">
-        <v>215.6568336</v>
+        <v>221.6473012</v>
       </c>
       <c r="N38">
-        <v>-29.0568336</v>
+        <v>-35.04730120000002</v>
       </c>
       <c r="O38">
-        <v>-9.298186752000001</v>
+        <v>-11.21513638400001</v>
       </c>
       <c r="P38">
-        <v>-19.75864684800001</v>
+        <v>-23.83216481600002</v>
       </c>
       <c r="Q38">
-        <v>26.44135315200001</v>
+        <v>22.367835184</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1385658901168246</v>
+        <v>0.1400383645631235</v>
       </c>
       <c r="T38">
-        <v>1.209050527451287</v>
+        <v>1.228241805664799</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2768843398246018</v>
+        <v>0.2694009792888017</v>
       </c>
       <c r="W38">
-        <v>0.1061533789137485</v>
+        <v>0.1072519362404039</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8652635619518806</v>
+        <v>0.8418780602775053</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1279073860837172</v>
+        <v>0.1289173860837172</v>
       </c>
       <c r="C39">
-        <v>1751.458048908477</v>
+        <v>1671.615398579802</v>
       </c>
       <c r="D39">
-        <v>3212.417048908477</v>
+        <v>3173.381398579801</v>
       </c>
       <c r="E39">
-        <v>1311.259</v>
+        <v>1352.066</v>
       </c>
       <c r="F39">
-        <v>1509.859</v>
+        <v>1550.666</v>
       </c>
       <c r="G39">
         <v>48.9</v>
@@ -4485,37 +4485,37 @@
         <v>186.6</v>
       </c>
       <c r="M39">
-        <v>221.6473012</v>
+        <v>227.6377688</v>
       </c>
       <c r="N39">
-        <v>-35.04730120000002</v>
+        <v>-41.03776880000001</v>
       </c>
       <c r="O39">
-        <v>-11.21513638400001</v>
+        <v>-13.132086016</v>
       </c>
       <c r="P39">
-        <v>-23.83216481600002</v>
+        <v>-27.90568278400001</v>
       </c>
       <c r="Q39">
-        <v>22.367835184</v>
+        <v>18.29431721600001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1400383645631235</v>
+        <v>0.1415583381851093</v>
       </c>
       <c r="T39">
-        <v>1.228241805664799</v>
+        <v>1.24805215736907</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.2694009792888017</v>
+        <v>0.2623114798338333</v>
       </c>
       <c r="W39">
-        <v>0.1072519362404039</v>
+        <v>0.1082926747603933</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8418780602775053</v>
+        <v>0.819723374480729</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1289173860837172</v>
+        <v>0.1527550575345736</v>
       </c>
       <c r="C40">
-        <v>1671.615398579802</v>
+        <v>923.5391500624828</v>
       </c>
       <c r="D40">
-        <v>3173.381398579801</v>
+        <v>2466.112150062483</v>
       </c>
       <c r="E40">
-        <v>1352.066</v>
+        <v>1392.873</v>
       </c>
       <c r="F40">
-        <v>1550.666</v>
+        <v>1591.473</v>
       </c>
       <c r="G40">
         <v>48.9</v>
@@ -4567,45 +4567,45 @@
         <v>186.6</v>
       </c>
       <c r="M40">
-        <v>227.6377688</v>
+        <v>319.5677784</v>
       </c>
       <c r="N40">
-        <v>-41.03776880000001</v>
+        <v>-132.9677784</v>
       </c>
       <c r="O40">
-        <v>-13.132086016</v>
+        <v>-42.54968908800001</v>
       </c>
       <c r="P40">
-        <v>-27.90568278400001</v>
+        <v>-90.41808931200001</v>
       </c>
       <c r="Q40">
-        <v>18.29431721600001</v>
+        <v>-44.21808931199999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1415583381851093</v>
+        <v>0.1460259690584003</v>
       </c>
       <c r="T40">
-        <v>1.24805215736907</v>
+        <v>1.30628036449356</v>
       </c>
       <c r="U40">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.2623114798338333</v>
+        <v>0.1868523801084196</v>
       </c>
       <c r="W40">
-        <v>0.1082926747603933</v>
+        <v>0.1632800420742294</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.819723374480729</v>
+        <v>0.5839136878388111</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1527550575345736</v>
+        <v>0.1543050575345736</v>
       </c>
       <c r="C41">
-        <v>923.5391500624828</v>
+        <v>847.5036186055147</v>
       </c>
       <c r="D41">
-        <v>2466.112150062483</v>
+        <v>2430.883618605515</v>
       </c>
       <c r="E41">
-        <v>1392.873</v>
+        <v>1433.68</v>
       </c>
       <c r="F41">
-        <v>1591.473</v>
+        <v>1632.28</v>
       </c>
       <c r="G41">
         <v>48.9</v>
@@ -4649,37 +4649,37 @@
         <v>186.6</v>
       </c>
       <c r="M41">
-        <v>319.5677784</v>
+        <v>327.761824</v>
       </c>
       <c r="N41">
-        <v>-132.9677784</v>
+        <v>-141.161824</v>
       </c>
       <c r="O41">
-        <v>-42.54968908800001</v>
+        <v>-45.17178368</v>
       </c>
       <c r="P41">
-        <v>-90.41808931200001</v>
+        <v>-95.99004031999999</v>
       </c>
       <c r="Q41">
-        <v>-44.21808931199999</v>
+        <v>-49.79004031999997</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1460259690584003</v>
+        <v>0.1476964018760403</v>
       </c>
       <c r="T41">
-        <v>1.30628036449356</v>
+        <v>1.328051703901786</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1868523801084196</v>
+        <v>0.1821810706057091</v>
       </c>
       <c r="W41">
-        <v>0.1632800420742294</v>
+        <v>0.1642180410223736</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5839136878388111</v>
+        <v>0.5693158456428409</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1543050575345736</v>
+        <v>0.1558550575345736</v>
       </c>
       <c r="C42">
-        <v>847.5036186055147</v>
+        <v>772.4603945441631</v>
       </c>
       <c r="D42">
-        <v>2430.883618605515</v>
+        <v>2396.647394544163</v>
       </c>
       <c r="E42">
-        <v>1433.68</v>
+        <v>1474.487</v>
       </c>
       <c r="F42">
-        <v>1632.28</v>
+        <v>1673.087</v>
       </c>
       <c r="G42">
         <v>48.9</v>
@@ -4731,37 +4731,37 @@
         <v>186.6</v>
       </c>
       <c r="M42">
-        <v>327.761824</v>
+        <v>335.9558696</v>
       </c>
       <c r="N42">
-        <v>-141.161824</v>
+        <v>-149.3558696</v>
       </c>
       <c r="O42">
-        <v>-45.17178368</v>
+        <v>-47.79387827200001</v>
       </c>
       <c r="P42">
-        <v>-95.99004031999999</v>
+        <v>-101.561991328</v>
       </c>
       <c r="Q42">
-        <v>-49.79004031999997</v>
+        <v>-55.361991328</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1476964018760403</v>
+        <v>0.1494234595349563</v>
       </c>
       <c r="T42">
-        <v>1.328051703901786</v>
+        <v>1.350561054815376</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1821810706057091</v>
+        <v>0.1777376298592284</v>
       </c>
       <c r="W42">
-        <v>0.1642180410223736</v>
+        <v>0.1651102839242669</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5693158456428409</v>
+        <v>0.5554300933100886</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1558550575345736</v>
+        <v>0.1574050575345736</v>
       </c>
       <c r="C43">
-        <v>772.4603945441631</v>
+        <v>698.3681336106022</v>
       </c>
       <c r="D43">
-        <v>2396.647394544163</v>
+        <v>2363.362133610602</v>
       </c>
       <c r="E43">
-        <v>1474.487</v>
+        <v>1515.294</v>
       </c>
       <c r="F43">
-        <v>1673.087</v>
+        <v>1713.894</v>
       </c>
       <c r="G43">
         <v>48.9</v>
@@ -4813,37 +4813,37 @@
         <v>186.6</v>
       </c>
       <c r="M43">
-        <v>335.9558696</v>
+        <v>344.1499152</v>
       </c>
       <c r="N43">
-        <v>-149.3558696</v>
+        <v>-157.5499152</v>
       </c>
       <c r="O43">
-        <v>-47.79387827200001</v>
+        <v>-50.415972864</v>
       </c>
       <c r="P43">
-        <v>-101.561991328</v>
+        <v>-107.133942336</v>
       </c>
       <c r="Q43">
-        <v>-55.361991328</v>
+        <v>-60.933942336</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1494234595349563</v>
+        <v>0.1512100709062486</v>
       </c>
       <c r="T43">
-        <v>1.350561054815376</v>
+        <v>1.373846590243227</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1777376298592284</v>
+        <v>0.1735057815292468</v>
       </c>
       <c r="W43">
-        <v>0.1651102839242669</v>
+        <v>0.1659600390689273</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5554300933100886</v>
+        <v>0.5422055672788961</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1574050575345737</v>
+        <v>0.1589550575345736</v>
       </c>
       <c r="C44">
-        <v>698.3681336106015</v>
+        <v>625.1877568750795</v>
       </c>
       <c r="D44">
-        <v>2363.362133610601</v>
+        <v>2330.988756875079</v>
       </c>
       <c r="E44">
-        <v>1515.294</v>
+        <v>1556.101</v>
       </c>
       <c r="F44">
-        <v>1713.894</v>
+        <v>1754.701</v>
       </c>
       <c r="G44">
         <v>48.9</v>
@@ -4895,37 +4895,37 @@
         <v>186.6</v>
       </c>
       <c r="M44">
-        <v>344.1499152</v>
+        <v>352.3439608</v>
       </c>
       <c r="N44">
-        <v>-157.5499152</v>
+        <v>-165.7439608</v>
       </c>
       <c r="O44">
-        <v>-50.41597286399999</v>
+        <v>-53.038067456</v>
       </c>
       <c r="P44">
-        <v>-107.133942336</v>
+        <v>-112.705893344</v>
       </c>
       <c r="Q44">
-        <v>-60.93394233599994</v>
+        <v>-66.50589334399999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1512100709062486</v>
+        <v>0.1530593703958319</v>
       </c>
       <c r="T44">
-        <v>1.373846590243227</v>
+        <v>1.39794916200188</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1735057815292468</v>
+        <v>0.169470763354148</v>
       </c>
       <c r="W44">
-        <v>0.1659600390689273</v>
+        <v>0.1667702707184871</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5422055672788961</v>
+        <v>0.5295961354817125</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1589550575345736</v>
+        <v>0.1605050575345737</v>
       </c>
       <c r="C45">
-        <v>625.1877568750795</v>
+        <v>552.8822976892895</v>
       </c>
       <c r="D45">
-        <v>2330.988756875079</v>
+        <v>2299.490297689289</v>
       </c>
       <c r="E45">
-        <v>1556.101</v>
+        <v>1596.908</v>
       </c>
       <c r="F45">
-        <v>1754.701</v>
+        <v>1795.508</v>
       </c>
       <c r="G45">
         <v>48.9</v>
@@ -4977,37 +4977,37 @@
         <v>186.6</v>
       </c>
       <c r="M45">
-        <v>352.3439608</v>
+        <v>360.5380064</v>
       </c>
       <c r="N45">
-        <v>-165.7439608</v>
+        <v>-173.9380064</v>
       </c>
       <c r="O45">
-        <v>-53.038067456</v>
+        <v>-55.66016204800001</v>
       </c>
       <c r="P45">
-        <v>-112.705893344</v>
+        <v>-118.277844352</v>
       </c>
       <c r="Q45">
-        <v>-66.50589334399999</v>
+        <v>-72.077844352</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1530593703958319</v>
+        <v>0.1549747162957575</v>
       </c>
       <c r="T45">
-        <v>1.39794916200188</v>
+        <v>1.422912539894771</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.169470763354148</v>
+        <v>0.1656191550960992</v>
       </c>
       <c r="W45">
-        <v>0.1667702707184871</v>
+        <v>0.1675436736567033</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5295961354817125</v>
+        <v>0.5175598596753099</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1605050575345737</v>
+        <v>0.1620550575345737</v>
       </c>
       <c r="C46">
-        <v>552.8822976892895</v>
+        <v>481.416760873733</v>
       </c>
       <c r="D46">
-        <v>2299.490297689289</v>
+        <v>2268.831760873733</v>
       </c>
       <c r="E46">
-        <v>1596.908</v>
+        <v>1637.715</v>
       </c>
       <c r="F46">
-        <v>1795.508</v>
+        <v>1836.315</v>
       </c>
       <c r="G46">
         <v>48.9</v>
@@ -5059,37 +5059,37 @@
         <v>186.6</v>
       </c>
       <c r="M46">
-        <v>360.5380064</v>
+        <v>368.732052</v>
       </c>
       <c r="N46">
-        <v>-173.9380064</v>
+        <v>-182.132052</v>
       </c>
       <c r="O46">
-        <v>-55.66016204800001</v>
+        <v>-58.28225664000001</v>
       </c>
       <c r="P46">
-        <v>-118.277844352</v>
+        <v>-123.84979536</v>
       </c>
       <c r="Q46">
-        <v>-72.077844352</v>
+        <v>-77.64979535999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1549747162957575</v>
+        <v>0.1569597111374985</v>
       </c>
       <c r="T46">
-        <v>1.422912539894771</v>
+        <v>1.448783676983767</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1656191550960992</v>
+        <v>0.161938729427297</v>
       </c>
       <c r="W46">
-        <v>0.1675436736567033</v>
+        <v>0.1682827031309988</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5175598596753099</v>
+        <v>0.5060585294603031</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1620550575345737</v>
+        <v>0.1804183343160976</v>
       </c>
       <c r="C47">
-        <v>481.416760873733</v>
+        <v>131.1185923245275</v>
       </c>
       <c r="D47">
-        <v>2268.831760873733</v>
+        <v>1959.340592324528</v>
       </c>
       <c r="E47">
-        <v>1637.715</v>
+        <v>1678.522</v>
       </c>
       <c r="F47">
-        <v>1836.315</v>
+        <v>1877.122</v>
       </c>
       <c r="G47">
         <v>48.9</v>
@@ -5141,45 +5141,45 @@
         <v>186.6</v>
       </c>
       <c r="M47">
-        <v>368.732052</v>
+        <v>442.6253676000001</v>
       </c>
       <c r="N47">
-        <v>-182.132052</v>
+        <v>-256.0253676000001</v>
       </c>
       <c r="O47">
-        <v>-58.28225664000001</v>
+        <v>-81.92811763200004</v>
       </c>
       <c r="P47">
-        <v>-123.84979536</v>
+        <v>-174.0972499680001</v>
       </c>
       <c r="Q47">
-        <v>-77.64979535999998</v>
+        <v>-127.897249968</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1569597111374985</v>
+        <v>0.1603391072354595</v>
       </c>
       <c r="T47">
-        <v>1.448783676983767</v>
+        <v>1.492828536894677</v>
       </c>
       <c r="U47">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.161938729427297</v>
+        <v>0.1349041522942301</v>
       </c>
       <c r="W47">
-        <v>0.1682827031309988</v>
+        <v>0.2039896008890205</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.5060585294603031</v>
+        <v>0.4215754759194691</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1804183343160976</v>
+        <v>0.1823183343160976</v>
       </c>
       <c r="C48">
-        <v>131.1185923245275</v>
+        <v>63.04238233844012</v>
       </c>
       <c r="D48">
-        <v>1959.340592324528</v>
+        <v>1932.07138233844</v>
       </c>
       <c r="E48">
-        <v>1678.522</v>
+        <v>1719.329</v>
       </c>
       <c r="F48">
-        <v>1877.122</v>
+        <v>1917.929</v>
       </c>
       <c r="G48">
         <v>48.9</v>
@@ -5223,37 +5223,37 @@
         <v>186.6</v>
       </c>
       <c r="M48">
-        <v>442.6253676000001</v>
+        <v>452.2476582</v>
       </c>
       <c r="N48">
-        <v>-256.0253676000001</v>
+        <v>-265.6476582</v>
       </c>
       <c r="O48">
-        <v>-81.92811763200004</v>
+        <v>-85.00725062400001</v>
       </c>
       <c r="P48">
-        <v>-174.0972499680001</v>
+        <v>-180.640407576</v>
       </c>
       <c r="Q48">
-        <v>-127.897249968</v>
+        <v>-134.440407576</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1603391072354595</v>
+        <v>0.1625002224663172</v>
       </c>
       <c r="T48">
-        <v>1.492828536894677</v>
+        <v>1.520995113062501</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1349041522942301</v>
+        <v>0.1320338511815869</v>
       </c>
       <c r="W48">
-        <v>0.2039896008890205</v>
+        <v>0.2046664178913818</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4215754759194691</v>
+        <v>0.4126057849424593</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1823183343160976</v>
+        <v>0.1842183343160976</v>
       </c>
       <c r="C49">
-        <v>63.04238233844012</v>
+        <v>-4.285205736691523</v>
       </c>
       <c r="D49">
-        <v>1932.07138233844</v>
+        <v>1905.550794263308</v>
       </c>
       <c r="E49">
-        <v>1719.329</v>
+        <v>1760.136</v>
       </c>
       <c r="F49">
-        <v>1917.929</v>
+        <v>1958.736</v>
       </c>
       <c r="G49">
         <v>48.9</v>
@@ -5305,37 +5305,37 @@
         <v>186.6</v>
       </c>
       <c r="M49">
-        <v>452.2476582</v>
+        <v>461.8699488</v>
       </c>
       <c r="N49">
-        <v>-265.6476582</v>
+        <v>-275.2699488000001</v>
       </c>
       <c r="O49">
-        <v>-85.00725062400001</v>
+        <v>-88.08638361600002</v>
       </c>
       <c r="P49">
-        <v>-180.640407576</v>
+        <v>-187.183565184</v>
       </c>
       <c r="Q49">
-        <v>-134.440407576</v>
+        <v>-140.983565184</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1625002224663172</v>
+        <v>0.1647444575137464</v>
       </c>
       <c r="T49">
-        <v>1.520995113062501</v>
+        <v>1.550245019082934</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1320338511815869</v>
+        <v>0.1292831459486372</v>
       </c>
       <c r="W49">
-        <v>0.2046664178913818</v>
+        <v>0.2053150341853114</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4126057849424593</v>
+        <v>0.4040098310894912</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1842183343160975</v>
+        <v>0.1861183343160975</v>
       </c>
       <c r="C50">
-        <v>-4.285205736690841</v>
+        <v>-70.8945823594363</v>
       </c>
       <c r="D50">
-        <v>1905.550794263309</v>
+        <v>1879.748417640564</v>
       </c>
       <c r="E50">
-        <v>1760.136</v>
+        <v>1800.943</v>
       </c>
       <c r="F50">
-        <v>1958.736</v>
+        <v>1999.543</v>
       </c>
       <c r="G50">
         <v>48.9</v>
@@ -5387,37 +5387,37 @@
         <v>186.6</v>
       </c>
       <c r="M50">
-        <v>461.8699488</v>
+        <v>471.4922394</v>
       </c>
       <c r="N50">
-        <v>-275.2699488</v>
+        <v>-284.8922394</v>
       </c>
       <c r="O50">
-        <v>-88.08638361599999</v>
+        <v>-91.165516608</v>
       </c>
       <c r="P50">
-        <v>-187.183565184</v>
+        <v>-193.726722792</v>
       </c>
       <c r="Q50">
-        <v>-140.983565184</v>
+        <v>-147.526722792</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1647444575137464</v>
+        <v>0.1670767017787218</v>
       </c>
       <c r="T50">
-        <v>1.550245019082934</v>
+        <v>1.580641980241423</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1292831459486372</v>
+        <v>0.126644714398665</v>
       </c>
       <c r="W50">
-        <v>0.2053150341853114</v>
+        <v>0.2059371763447948</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4040098310894914</v>
+        <v>0.3957647324958282</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1861183343160975</v>
+        <v>0.1880183343160975</v>
       </c>
       <c r="C51">
-        <v>-70.8945823594363</v>
+        <v>-136.8145328850624</v>
       </c>
       <c r="D51">
-        <v>1879.748417640564</v>
+        <v>1854.635467114937</v>
       </c>
       <c r="E51">
-        <v>1800.943</v>
+        <v>1841.75</v>
       </c>
       <c r="F51">
-        <v>1999.543</v>
+        <v>2040.35</v>
       </c>
       <c r="G51">
         <v>48.9</v>
@@ -5469,37 +5469,37 @@
         <v>186.6</v>
       </c>
       <c r="M51">
-        <v>471.4922394</v>
+        <v>481.11453</v>
       </c>
       <c r="N51">
-        <v>-284.8922394</v>
+        <v>-294.51453</v>
       </c>
       <c r="O51">
-        <v>-91.165516608</v>
+        <v>-94.24464960000002</v>
       </c>
       <c r="P51">
-        <v>-193.726722792</v>
+        <v>-200.2698804</v>
       </c>
       <c r="Q51">
-        <v>-147.526722792</v>
+        <v>-154.0698804</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1670767017787218</v>
+        <v>0.1695022358142962</v>
       </c>
       <c r="T51">
-        <v>1.580641980241423</v>
+        <v>1.612254819846251</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.126644714398665</v>
+        <v>0.1241118201106917</v>
       </c>
       <c r="W51">
-        <v>0.2059371763447948</v>
+        <v>0.2065344328178989</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3957647324958282</v>
+        <v>0.3878494378459116</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1880183343160975</v>
+        <v>0.1899183343160976</v>
       </c>
       <c r="C52">
-        <v>-136.8145328850624</v>
+        <v>-202.0723246891753</v>
       </c>
       <c r="D52">
-        <v>1854.635467114937</v>
+        <v>1830.184675310825</v>
       </c>
       <c r="E52">
-        <v>1841.75</v>
+        <v>1882.557</v>
       </c>
       <c r="F52">
-        <v>2040.35</v>
+        <v>2081.157</v>
       </c>
       <c r="G52">
         <v>48.9</v>
@@ -5551,37 +5551,37 @@
         <v>186.6</v>
       </c>
       <c r="M52">
-        <v>481.11453</v>
+        <v>490.7368206</v>
       </c>
       <c r="N52">
-        <v>-294.51453</v>
+        <v>-304.1368206000001</v>
       </c>
       <c r="O52">
-        <v>-94.24464960000002</v>
+        <v>-97.32378259200003</v>
       </c>
       <c r="P52">
-        <v>-200.2698804</v>
+        <v>-206.813038008</v>
       </c>
       <c r="Q52">
-        <v>-154.0698804</v>
+        <v>-160.613038008</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1695022358142962</v>
+        <v>0.1720267712390778</v>
       </c>
       <c r="T52">
-        <v>1.612254819846251</v>
+        <v>1.64515797943495</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1241118201106917</v>
+        <v>0.1216782550104821</v>
       </c>
       <c r="W52">
-        <v>0.2065344328178989</v>
+        <v>0.2071082674685283</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3878494378459116</v>
+        <v>0.3802445469077564</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1899183343160976</v>
+        <v>0.1918183343160976</v>
       </c>
       <c r="C53">
-        <v>-202.0723246891753</v>
+        <v>-266.6938059279687</v>
       </c>
       <c r="D53">
-        <v>1830.184675310825</v>
+        <v>1806.370194072031</v>
       </c>
       <c r="E53">
-        <v>1882.557</v>
+        <v>1923.364</v>
       </c>
       <c r="F53">
-        <v>2081.157</v>
+        <v>2121.964</v>
       </c>
       <c r="G53">
         <v>48.9</v>
@@ -5633,37 +5633,37 @@
         <v>186.6</v>
       </c>
       <c r="M53">
-        <v>490.7368206</v>
+        <v>500.3591112</v>
       </c>
       <c r="N53">
-        <v>-304.1368206000001</v>
+        <v>-313.7591112</v>
       </c>
       <c r="O53">
-        <v>-97.32378259200003</v>
+        <v>-100.402915584</v>
       </c>
       <c r="P53">
-        <v>-206.813038008</v>
+        <v>-213.356195616</v>
       </c>
       <c r="Q53">
-        <v>-160.613038008</v>
+        <v>-167.156195616</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1720267712390778</v>
+        <v>0.1746564956398919</v>
       </c>
       <c r="T53">
-        <v>1.64515797943495</v>
+        <v>1.679432104006512</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1216782550104821</v>
+        <v>0.1193382885679728</v>
       </c>
       <c r="W53">
-        <v>0.2071082674685283</v>
+        <v>0.207660031555672</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3802445469077564</v>
+        <v>0.3729321517749151</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1918183343160976</v>
+        <v>0.1937183343160976</v>
       </c>
       <c r="C54">
-        <v>-266.6938059279687</v>
+        <v>-330.703496687064</v>
       </c>
       <c r="D54">
-        <v>1806.370194072031</v>
+        <v>1783.167503312936</v>
       </c>
       <c r="E54">
-        <v>1923.364</v>
+        <v>1964.171</v>
       </c>
       <c r="F54">
-        <v>2121.964</v>
+        <v>2162.771</v>
       </c>
       <c r="G54">
         <v>48.9</v>
@@ -5715,37 +5715,37 @@
         <v>186.6</v>
       </c>
       <c r="M54">
-        <v>500.3591112</v>
+        <v>509.9814018000001</v>
       </c>
       <c r="N54">
-        <v>-313.7591112</v>
+        <v>-323.3814018</v>
       </c>
       <c r="O54">
-        <v>-100.402915584</v>
+        <v>-103.482048576</v>
       </c>
       <c r="P54">
-        <v>-213.356195616</v>
+        <v>-219.899353224</v>
       </c>
       <c r="Q54">
-        <v>-167.156195616</v>
+        <v>-173.699353224</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1746564956398919</v>
+        <v>0.1773981232066981</v>
       </c>
       <c r="T54">
-        <v>1.679432104006512</v>
+        <v>1.715164701964097</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1193382885679728</v>
+        <v>0.1170866227459356</v>
       </c>
       <c r="W54">
-        <v>0.207660031555672</v>
+        <v>0.2081909743565084</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3729321517749151</v>
+        <v>0.3658956960810488</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1937183343160976</v>
+        <v>0.1956183343160975</v>
       </c>
       <c r="C55">
-        <v>-330.703496687064</v>
+        <v>-394.1246731946351</v>
       </c>
       <c r="D55">
-        <v>1783.167503312936</v>
+        <v>1760.553326805365</v>
       </c>
       <c r="E55">
-        <v>1964.171</v>
+        <v>2004.978</v>
       </c>
       <c r="F55">
-        <v>2162.771</v>
+        <v>2203.578</v>
       </c>
       <c r="G55">
         <v>48.9</v>
@@ -5797,37 +5797,37 @@
         <v>186.6</v>
       </c>
       <c r="M55">
-        <v>509.9814018000001</v>
+        <v>519.6036924</v>
       </c>
       <c r="N55">
-        <v>-323.3814018</v>
+        <v>-333.0036924</v>
       </c>
       <c r="O55">
-        <v>-103.482048576</v>
+        <v>-106.561181568</v>
       </c>
       <c r="P55">
-        <v>-219.899353224</v>
+        <v>-226.442510832</v>
       </c>
       <c r="Q55">
-        <v>-173.699353224</v>
+        <v>-180.242510832</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1773981232066981</v>
+        <v>0.1802589519720611</v>
       </c>
       <c r="T55">
-        <v>1.715164701964097</v>
+        <v>1.75245089113723</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1170866227459356</v>
+        <v>0.1149183519543442</v>
       </c>
       <c r="W55">
-        <v>0.2081909743565084</v>
+        <v>0.2087022526091656</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3658956960810488</v>
+        <v>0.3591198498573257</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1956183343160975</v>
+        <v>0.1975183343160976</v>
       </c>
       <c r="C56">
-        <v>-394.1246731946351</v>
+        <v>-456.9794457068288</v>
       </c>
       <c r="D56">
-        <v>1760.553326805365</v>
+        <v>1738.505554293171</v>
       </c>
       <c r="E56">
-        <v>2004.978</v>
+        <v>2045.785</v>
       </c>
       <c r="F56">
-        <v>2203.578</v>
+        <v>2244.385</v>
       </c>
       <c r="G56">
         <v>48.9</v>
@@ -5879,37 +5879,37 @@
         <v>186.6</v>
       </c>
       <c r="M56">
-        <v>519.6036924</v>
+        <v>529.225983</v>
       </c>
       <c r="N56">
-        <v>-333.0036924</v>
+        <v>-342.625983</v>
       </c>
       <c r="O56">
-        <v>-106.561181568</v>
+        <v>-109.64031456</v>
       </c>
       <c r="P56">
-        <v>-226.442510832</v>
+        <v>-232.98566844</v>
       </c>
       <c r="Q56">
-        <v>-180.242510832</v>
+        <v>-186.78566844</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1802589519720611</v>
+        <v>0.1832469286825514</v>
       </c>
       <c r="T56">
-        <v>1.75245089113723</v>
+        <v>1.791394244273613</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1149183519543442</v>
+        <v>0.1128289273733561</v>
       </c>
       <c r="W56">
-        <v>0.2087022526091656</v>
+        <v>0.2091949389253626</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3591198498573257</v>
+        <v>0.3525903980417379</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1975183343160976</v>
+        <v>0.1994183343160976</v>
       </c>
       <c r="C57">
-        <v>-456.9794457068288</v>
+        <v>-519.2888306133082</v>
       </c>
       <c r="D57">
-        <v>1738.505554293171</v>
+        <v>1717.003169386692</v>
       </c>
       <c r="E57">
-        <v>2045.785</v>
+        <v>2086.592</v>
       </c>
       <c r="F57">
-        <v>2244.385</v>
+        <v>2285.192</v>
       </c>
       <c r="G57">
         <v>48.9</v>
@@ -5961,37 +5961,37 @@
         <v>186.6</v>
       </c>
       <c r="M57">
-        <v>529.225983</v>
+        <v>538.8482736</v>
       </c>
       <c r="N57">
-        <v>-342.625983</v>
+        <v>-352.2482735999999</v>
       </c>
       <c r="O57">
-        <v>-109.64031456</v>
+        <v>-112.719447552</v>
       </c>
       <c r="P57">
-        <v>-232.98566844</v>
+        <v>-239.528826048</v>
       </c>
       <c r="Q57">
-        <v>-186.78566844</v>
+        <v>-193.3288260479999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1832469286825514</v>
+        <v>0.1863707225162457</v>
       </c>
       <c r="T57">
-        <v>1.791394244273613</v>
+        <v>1.832107749825286</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1128289273733561</v>
+        <v>0.1108141250988319</v>
       </c>
       <c r="W57">
-        <v>0.2091949389253626</v>
+        <v>0.2096700293016954</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3525903980417379</v>
+        <v>0.3462941409338498</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1994183343160976</v>
+        <v>0.2013183343160976</v>
       </c>
       <c r="C58">
-        <v>-519.2888306133082</v>
+        <v>-581.0728172572367</v>
       </c>
       <c r="D58">
-        <v>1717.003169386692</v>
+        <v>1696.026182742763</v>
       </c>
       <c r="E58">
-        <v>2086.592</v>
+        <v>2127.399</v>
       </c>
       <c r="F58">
-        <v>2285.192</v>
+        <v>2325.999</v>
       </c>
       <c r="G58">
         <v>48.9</v>
@@ -6043,37 +6043,37 @@
         <v>186.6</v>
       </c>
       <c r="M58">
-        <v>538.8482736</v>
+        <v>548.4705642000001</v>
       </c>
       <c r="N58">
-        <v>-352.2482735999999</v>
+        <v>-361.8705642000001</v>
       </c>
       <c r="O58">
-        <v>-112.719447552</v>
+        <v>-115.798580544</v>
       </c>
       <c r="P58">
-        <v>-239.528826048</v>
+        <v>-246.0719836560001</v>
       </c>
       <c r="Q58">
-        <v>-193.3288260479999</v>
+        <v>-199.8719836560001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1863707225162457</v>
+        <v>0.189639809086391</v>
       </c>
       <c r="T58">
-        <v>1.832107749825286</v>
+        <v>1.874714906797967</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1108141250988319</v>
+        <v>0.1088700176409576</v>
       </c>
       <c r="W58">
-        <v>0.2096700293016954</v>
+        <v>0.2101284498402622</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3462941409338498</v>
+        <v>0.3402188051279926</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2013183343160976</v>
+        <v>0.2032183343160976</v>
       </c>
       <c r="C59">
-        <v>-581.0728172572367</v>
+        <v>-642.3504299162457</v>
       </c>
       <c r="D59">
-        <v>1696.026182742763</v>
+        <v>1675.555570083754</v>
       </c>
       <c r="E59">
-        <v>2127.399</v>
+        <v>2168.206</v>
       </c>
       <c r="F59">
-        <v>2325.999</v>
+        <v>2366.806</v>
       </c>
       <c r="G59">
         <v>48.9</v>
@@ -6125,37 +6125,37 @@
         <v>186.6</v>
       </c>
       <c r="M59">
-        <v>548.4705642000001</v>
+        <v>558.0928548000001</v>
       </c>
       <c r="N59">
-        <v>-361.8705642000001</v>
+        <v>-371.4928548</v>
       </c>
       <c r="O59">
-        <v>-115.798580544</v>
+        <v>-118.877713536</v>
       </c>
       <c r="P59">
-        <v>-246.0719836560001</v>
+        <v>-252.615141264</v>
       </c>
       <c r="Q59">
-        <v>-199.8719836560001</v>
+        <v>-206.415141264</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.189639809086391</v>
+        <v>0.1930645664455908</v>
       </c>
       <c r="T59">
-        <v>1.874714906797967</v>
+        <v>1.919350976007443</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1088700176409576</v>
+        <v>0.106992948371286</v>
       </c>
       <c r="W59">
-        <v>0.2101284498402622</v>
+        <v>0.2105710627740508</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3402188051279926</v>
+        <v>0.3343529636602687</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2032183343160976</v>
+        <v>0.2051183343160976</v>
       </c>
       <c r="C60">
-        <v>-642.3504299162453</v>
+        <v>-703.1397853483752</v>
       </c>
       <c r="D60">
-        <v>1675.555570083754</v>
+        <v>1655.573214651625</v>
       </c>
       <c r="E60">
-        <v>2168.206</v>
+        <v>2209.013</v>
       </c>
       <c r="F60">
-        <v>2366.806</v>
+        <v>2407.613</v>
       </c>
       <c r="G60">
         <v>48.9</v>
@@ -6207,37 +6207,37 @@
         <v>186.6</v>
       </c>
       <c r="M60">
-        <v>558.0928547999999</v>
+        <v>567.7151454</v>
       </c>
       <c r="N60">
-        <v>-371.4928547999999</v>
+        <v>-381.1151454</v>
       </c>
       <c r="O60">
-        <v>-118.877713536</v>
+        <v>-121.956846528</v>
       </c>
       <c r="P60">
-        <v>-252.6151412639999</v>
+        <v>-259.158298872</v>
       </c>
       <c r="Q60">
-        <v>-206.4151412639999</v>
+        <v>-212.958298872</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1930645664455907</v>
+        <v>0.1966563851393856</v>
       </c>
       <c r="T60">
-        <v>1.919350976007442</v>
+        <v>1.966164414446648</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.106992948371286</v>
+        <v>0.1051795085683828</v>
       </c>
       <c r="W60">
-        <v>0.2105710627740508</v>
+        <v>0.2109986718795753</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3343529636602688</v>
+        <v>0.3286859642761963</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2051183343160976</v>
+        <v>0.2070183343160975</v>
       </c>
       <c r="C61">
-        <v>-703.1397853483752</v>
+        <v>-763.4581462688427</v>
       </c>
       <c r="D61">
-        <v>1655.573214651625</v>
+        <v>1636.061853731157</v>
       </c>
       <c r="E61">
-        <v>2209.013</v>
+        <v>2249.82</v>
       </c>
       <c r="F61">
-        <v>2407.613</v>
+        <v>2448.42</v>
       </c>
       <c r="G61">
         <v>48.9</v>
@@ -6289,37 +6289,37 @@
         <v>186.6</v>
       </c>
       <c r="M61">
-        <v>567.7151454</v>
+        <v>577.3374359999999</v>
       </c>
       <c r="N61">
-        <v>-381.1151454</v>
+        <v>-390.7374359999999</v>
       </c>
       <c r="O61">
-        <v>-121.956846528</v>
+        <v>-125.03597952</v>
       </c>
       <c r="P61">
-        <v>-259.158298872</v>
+        <v>-265.7014564799999</v>
       </c>
       <c r="Q61">
-        <v>-212.958298872</v>
+        <v>-219.5014564799999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1966563851393856</v>
+        <v>0.2004277947678702</v>
       </c>
       <c r="T61">
-        <v>1.966164414446648</v>
+        <v>2.015318524807814</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1051795085683828</v>
+        <v>0.1034265167589098</v>
       </c>
       <c r="W61">
-        <v>0.2109986718795753</v>
+        <v>0.2114120273482491</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3286859642761963</v>
+        <v>0.3232078648715931</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2070183343160975</v>
+        <v>0.2089183343160976</v>
       </c>
       <c r="C62">
-        <v>-763.4581462688427</v>
+        <v>-823.3219710894389</v>
       </c>
       <c r="D62">
-        <v>1636.061853731157</v>
+        <v>1617.005028910561</v>
       </c>
       <c r="E62">
-        <v>2249.82</v>
+        <v>2290.627</v>
       </c>
       <c r="F62">
-        <v>2448.42</v>
+        <v>2489.227</v>
       </c>
       <c r="G62">
         <v>48.9</v>
@@ -6371,37 +6371,37 @@
         <v>186.6</v>
       </c>
       <c r="M62">
-        <v>577.3374359999999</v>
+        <v>586.9597266</v>
       </c>
       <c r="N62">
-        <v>-390.7374359999999</v>
+        <v>-400.3597265999999</v>
       </c>
       <c r="O62">
-        <v>-125.03597952</v>
+        <v>-128.115112512</v>
       </c>
       <c r="P62">
-        <v>-265.7014564799999</v>
+        <v>-272.2446140879999</v>
       </c>
       <c r="Q62">
-        <v>-219.5014564799999</v>
+        <v>-226.0446140879999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2004277947678702</v>
+        <v>0.2043926100183285</v>
       </c>
       <c r="T62">
-        <v>2.015318524807814</v>
+        <v>2.066993358777246</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1034265167589098</v>
+        <v>0.1017310000907309</v>
       </c>
       <c r="W62">
-        <v>0.2114120273482491</v>
+        <v>0.2118118301786057</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3232078648715931</v>
+        <v>0.3179093752835342</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2089183343160976</v>
+        <v>0.2108183343160975</v>
       </c>
       <c r="C63">
-        <v>-823.3219710894389</v>
+        <v>-882.7469602217548</v>
       </c>
       <c r="D63">
-        <v>1617.005028910561</v>
+        <v>1598.387039778245</v>
       </c>
       <c r="E63">
-        <v>2290.627</v>
+        <v>2331.434</v>
       </c>
       <c r="F63">
-        <v>2489.227</v>
+        <v>2530.034</v>
       </c>
       <c r="G63">
         <v>48.9</v>
@@ -6453,37 +6453,37 @@
         <v>186.6</v>
       </c>
       <c r="M63">
-        <v>586.9597266</v>
+        <v>596.5820172</v>
       </c>
       <c r="N63">
-        <v>-400.3597265999999</v>
+        <v>-409.9820172</v>
       </c>
       <c r="O63">
-        <v>-128.115112512</v>
+        <v>-131.194245504</v>
       </c>
       <c r="P63">
-        <v>-272.2446140879999</v>
+        <v>-278.787771696</v>
       </c>
       <c r="Q63">
-        <v>-226.0446140879999</v>
+        <v>-232.587771696</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2043926100183285</v>
+        <v>0.2085660997556529</v>
       </c>
       <c r="T63">
-        <v>2.066993358777246</v>
+        <v>2.121387920850331</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1017310000907309</v>
+        <v>0.1000901775086224</v>
       </c>
       <c r="W63">
-        <v>0.2118118301786057</v>
+        <v>0.2121987361434668</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3179093752835342</v>
+        <v>0.3127818047144449</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2108183343160975</v>
+        <v>0.2127183343160975</v>
       </c>
       <c r="C64">
-        <v>-882.7469602217548</v>
+        <v>-941.7480992180595</v>
       </c>
       <c r="D64">
-        <v>1598.387039778245</v>
+        <v>1580.19290078194</v>
       </c>
       <c r="E64">
-        <v>2331.434</v>
+        <v>2372.241</v>
       </c>
       <c r="F64">
-        <v>2530.034</v>
+        <v>2570.841</v>
       </c>
       <c r="G64">
         <v>48.9</v>
@@ -6535,37 +6535,37 @@
         <v>186.6</v>
       </c>
       <c r="M64">
-        <v>596.5820172</v>
+        <v>606.2043078</v>
       </c>
       <c r="N64">
-        <v>-409.9820172</v>
+        <v>-419.6043078</v>
       </c>
       <c r="O64">
-        <v>-131.194245504</v>
+        <v>-134.273378496</v>
       </c>
       <c r="P64">
-        <v>-278.787771696</v>
+        <v>-285.330929304</v>
       </c>
       <c r="Q64">
-        <v>-232.587771696</v>
+        <v>-239.130929304</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2085660997556529</v>
+        <v>0.2129651835328327</v>
       </c>
       <c r="T64">
-        <v>2.121387920850331</v>
+        <v>2.178722729521962</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1000901775086224</v>
+        <v>0.09850144453229502</v>
       </c>
       <c r="W64">
-        <v>0.2121987361434668</v>
+        <v>0.2125733593792848</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3127818047144449</v>
+        <v>0.307817014163422</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2127183343160975</v>
+        <v>0.2146183343160975</v>
       </c>
       <c r="C65">
-        <v>-941.7480992180595</v>
+        <v>-1000.339698998934</v>
       </c>
       <c r="D65">
-        <v>1580.19290078194</v>
+        <v>1562.408301001066</v>
       </c>
       <c r="E65">
-        <v>2372.241</v>
+        <v>2413.048</v>
       </c>
       <c r="F65">
-        <v>2570.841</v>
+        <v>2611.648</v>
       </c>
       <c r="G65">
         <v>48.9</v>
@@ -6617,37 +6617,37 @@
         <v>186.6</v>
       </c>
       <c r="M65">
-        <v>606.2043078</v>
+        <v>615.8265984000001</v>
       </c>
       <c r="N65">
-        <v>-419.6043078</v>
+        <v>-429.2265984000001</v>
       </c>
       <c r="O65">
-        <v>-134.273378496</v>
+        <v>-137.352511488</v>
       </c>
       <c r="P65">
-        <v>-285.330929304</v>
+        <v>-291.8740869120001</v>
       </c>
       <c r="Q65">
-        <v>-239.130929304</v>
+        <v>-245.674086912</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2129651835328327</v>
+        <v>0.2176086608531892</v>
       </c>
       <c r="T65">
-        <v>2.178722729521962</v>
+        <v>2.239242805342016</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09850144453229502</v>
+        <v>0.0969623594614779</v>
       </c>
       <c r="W65">
-        <v>0.2125733593792848</v>
+        <v>0.2129362756389835</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.307817014163422</v>
+        <v>0.3030073733171185</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2146183343160975</v>
+        <v>0.2165183343160976</v>
       </c>
       <c r="C66">
-        <v>-1000.339698998934</v>
+        <v>-1058.535433394653</v>
       </c>
       <c r="D66">
-        <v>1562.408301001066</v>
+        <v>1545.019566605347</v>
       </c>
       <c r="E66">
-        <v>2413.048</v>
+        <v>2453.855</v>
       </c>
       <c r="F66">
-        <v>2611.648</v>
+        <v>2652.455</v>
       </c>
       <c r="G66">
         <v>48.9</v>
@@ -6699,37 +6699,37 @@
         <v>186.6</v>
       </c>
       <c r="M66">
-        <v>615.8265984000001</v>
+        <v>625.448889</v>
       </c>
       <c r="N66">
-        <v>-429.2265984000001</v>
+        <v>-438.848889</v>
       </c>
       <c r="O66">
-        <v>-137.352511488</v>
+        <v>-140.43164448</v>
       </c>
       <c r="P66">
-        <v>-291.8740869120001</v>
+        <v>-298.41724452</v>
       </c>
       <c r="Q66">
-        <v>-245.674086912</v>
+        <v>-252.21724452</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2176086608531892</v>
+        <v>0.2225174797347089</v>
       </c>
       <c r="T66">
-        <v>2.239242805342016</v>
+        <v>2.303221171208931</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0969623594614779</v>
+        <v>0.09547063085437825</v>
       </c>
       <c r="W66">
-        <v>0.2129362756389835</v>
+        <v>0.2132880252445376</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3030073733171185</v>
+        <v>0.2983457214199321</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2165183343160976</v>
+        <v>0.2184183343160976</v>
       </c>
       <c r="C67">
-        <v>-1058.535433394653</v>
+        <v>-1116.348374207258</v>
       </c>
       <c r="D67">
-        <v>1545.019566605347</v>
+        <v>1528.013625792742</v>
       </c>
       <c r="E67">
-        <v>2453.855</v>
+        <v>2494.662</v>
       </c>
       <c r="F67">
-        <v>2652.455</v>
+        <v>2693.262</v>
       </c>
       <c r="G67">
         <v>48.9</v>
@@ -6781,37 +6781,37 @@
         <v>186.6</v>
       </c>
       <c r="M67">
-        <v>625.448889</v>
+        <v>635.0711796000001</v>
       </c>
       <c r="N67">
-        <v>-438.848889</v>
+        <v>-448.4711796</v>
       </c>
       <c r="O67">
-        <v>-140.43164448</v>
+        <v>-143.510777472</v>
       </c>
       <c r="P67">
-        <v>-298.41724452</v>
+        <v>-304.9604021280001</v>
       </c>
       <c r="Q67">
-        <v>-252.21724452</v>
+        <v>-258.760402128</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2225174797347089</v>
+        <v>0.2277150526680827</v>
       </c>
       <c r="T67">
-        <v>2.303221171208931</v>
+        <v>2.370962970362135</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09547063085437825</v>
+        <v>0.09402410614446342</v>
       </c>
       <c r="W67">
-        <v>0.2132880252445376</v>
+        <v>0.2136291157711355</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2983457214199321</v>
+        <v>0.2938253317014482</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2184183343160976</v>
+        <v>0.2203183343160976</v>
       </c>
       <c r="C68">
-        <v>-1116.348374207258</v>
+        <v>-1173.7910239823</v>
       </c>
       <c r="D68">
-        <v>1528.013625792742</v>
+        <v>1511.3779760177</v>
       </c>
       <c r="E68">
-        <v>2494.662</v>
+        <v>2535.469</v>
       </c>
       <c r="F68">
-        <v>2693.262</v>
+        <v>2734.069</v>
       </c>
       <c r="G68">
         <v>48.9</v>
@@ -6863,37 +6863,37 @@
         <v>186.6</v>
       </c>
       <c r="M68">
-        <v>635.0711796000001</v>
+        <v>644.6934702</v>
       </c>
       <c r="N68">
-        <v>-448.4711796</v>
+        <v>-458.0934702</v>
       </c>
       <c r="O68">
-        <v>-143.510777472</v>
+        <v>-146.589910464</v>
       </c>
       <c r="P68">
-        <v>-304.9604021280001</v>
+        <v>-311.5035597359999</v>
       </c>
       <c r="Q68">
-        <v>-258.760402128</v>
+        <v>-265.3035597359999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2277150526680827</v>
+        <v>0.233227630021661</v>
       </c>
       <c r="T68">
-        <v>2.370962970362135</v>
+        <v>2.442810333100382</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09402410614446342</v>
+        <v>0.09262076127663563</v>
       </c>
       <c r="W68">
-        <v>0.2136291157711355</v>
+        <v>0.2139600244909693</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2938253317014482</v>
+        <v>0.2894398789894863</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2203183343160976</v>
+        <v>0.2222183343160976</v>
       </c>
       <c r="C69">
-        <v>-1173.7910239823</v>
+        <v>-1230.87534666288</v>
       </c>
       <c r="D69">
-        <v>1511.3779760177</v>
+        <v>1495.10065333712</v>
       </c>
       <c r="E69">
-        <v>2535.469</v>
+        <v>2576.276</v>
       </c>
       <c r="F69">
-        <v>2734.069</v>
+        <v>2774.876</v>
       </c>
       <c r="G69">
         <v>48.9</v>
@@ -6945,37 +6945,37 @@
         <v>186.6</v>
       </c>
       <c r="M69">
-        <v>644.6934702</v>
+        <v>654.3157608</v>
       </c>
       <c r="N69">
-        <v>-458.0934702</v>
+        <v>-467.7157608</v>
       </c>
       <c r="O69">
-        <v>-146.589910464</v>
+        <v>-149.669043456</v>
       </c>
       <c r="P69">
-        <v>-311.5035597359999</v>
+        <v>-318.046717344</v>
       </c>
       <c r="Q69">
-        <v>-265.3035597359999</v>
+        <v>-271.846717344</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.233227630021661</v>
+        <v>0.2390847434598379</v>
       </c>
       <c r="T69">
-        <v>2.442810333100382</v>
+        <v>2.519148156009768</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09262076127663563</v>
+        <v>0.09125869125786157</v>
       </c>
       <c r="W69">
-        <v>0.2139600244909693</v>
+        <v>0.2142812006013962</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2894398789894863</v>
+        <v>0.2851834101808174</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2222183343160976</v>
+        <v>0.2241183343160976</v>
       </c>
       <c r="C70">
-        <v>-1230.87534666288</v>
+        <v>-1287.612796283977</v>
       </c>
       <c r="D70">
-        <v>1495.10065333712</v>
+        <v>1479.170203716023</v>
       </c>
       <c r="E70">
-        <v>2576.276</v>
+        <v>2617.083</v>
       </c>
       <c r="F70">
-        <v>2774.876</v>
+        <v>2815.683</v>
       </c>
       <c r="G70">
         <v>48.9</v>
@@ -7027,37 +7027,37 @@
         <v>186.6</v>
       </c>
       <c r="M70">
-        <v>654.3157608</v>
+        <v>663.9380514000001</v>
       </c>
       <c r="N70">
-        <v>-467.7157608</v>
+        <v>-477.3380514</v>
       </c>
       <c r="O70">
-        <v>-149.669043456</v>
+        <v>-152.748176448</v>
       </c>
       <c r="P70">
-        <v>-318.046717344</v>
+        <v>-324.5898749520001</v>
       </c>
       <c r="Q70">
-        <v>-271.846717344</v>
+        <v>-278.389874952</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2390847434598379</v>
+        <v>0.2453197351843488</v>
       </c>
       <c r="T70">
-        <v>2.519148156009768</v>
+        <v>2.600410999752019</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09125869125786157</v>
+        <v>0.08993610152948675</v>
       </c>
       <c r="W70">
-        <v>0.2142812006013962</v>
+        <v>0.214593067259347</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2851834101808174</v>
+        <v>0.2810503172796461</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2241183343160976</v>
+        <v>0.2260183343160976</v>
       </c>
       <c r="C71">
-        <v>-1287.612796283977</v>
+        <v>-1344.014343851658</v>
       </c>
       <c r="D71">
-        <v>1479.170203716023</v>
+        <v>1463.575656148342</v>
       </c>
       <c r="E71">
-        <v>2617.083</v>
+        <v>2657.89</v>
       </c>
       <c r="F71">
-        <v>2815.683</v>
+        <v>2856.49</v>
       </c>
       <c r="G71">
         <v>48.9</v>
@@ -7109,37 +7109,37 @@
         <v>186.6</v>
       </c>
       <c r="M71">
-        <v>663.9380514000001</v>
+        <v>673.5603420000001</v>
       </c>
       <c r="N71">
-        <v>-477.3380514</v>
+        <v>-486.9603420000001</v>
       </c>
       <c r="O71">
-        <v>-152.748176448</v>
+        <v>-155.82730944</v>
       </c>
       <c r="P71">
-        <v>-324.5898749520001</v>
+        <v>-331.1330325600001</v>
       </c>
       <c r="Q71">
-        <v>-278.389874952</v>
+        <v>-284.93303256</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2453197351843488</v>
+        <v>0.2519703930238271</v>
       </c>
       <c r="T71">
-        <v>2.600410999752019</v>
+        <v>2.687091366410419</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08993610152948675</v>
+        <v>0.08865130007906551</v>
       </c>
       <c r="W71">
-        <v>0.214593067259347</v>
+        <v>0.2148960234413564</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2810503172796461</v>
+        <v>0.2770353127470797</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2260183343160976</v>
+        <v>0.2279183343160976</v>
       </c>
       <c r="C72">
-        <v>-1344.014343851658</v>
+        <v>-1400.090502539741</v>
       </c>
       <c r="D72">
-        <v>1463.575656148342</v>
+        <v>1448.306497460259</v>
       </c>
       <c r="E72">
-        <v>2657.89</v>
+        <v>2698.697</v>
       </c>
       <c r="F72">
-        <v>2856.49</v>
+        <v>2897.297</v>
       </c>
       <c r="G72">
         <v>48.9</v>
@@ -7191,37 +7191,37 @@
         <v>186.6</v>
       </c>
       <c r="M72">
-        <v>673.5603420000001</v>
+        <v>683.1826326</v>
       </c>
       <c r="N72">
-        <v>-486.9603420000001</v>
+        <v>-496.5826326</v>
       </c>
       <c r="O72">
-        <v>-155.82730944</v>
+        <v>-158.906442432</v>
       </c>
       <c r="P72">
-        <v>-331.1330325600001</v>
+        <v>-337.676190168</v>
       </c>
       <c r="Q72">
-        <v>-284.93303256</v>
+        <v>-291.476190168</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2519703930238271</v>
+        <v>0.2590797169212005</v>
       </c>
       <c r="T72">
-        <v>2.687091366410419</v>
+        <v>2.77974968939009</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08865130007906551</v>
+        <v>0.087402690218797</v>
       </c>
       <c r="W72">
-        <v>0.2148960234413564</v>
+        <v>0.2151904456464077</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2770353127470797</v>
+        <v>0.2731334069337407</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2279183343160976</v>
+        <v>0.2298183343160976</v>
       </c>
       <c r="C73">
-        <v>-1400.09050253974</v>
+        <v>-1455.851351325523</v>
       </c>
       <c r="D73">
-        <v>1448.306497460259</v>
+        <v>1433.352648674477</v>
       </c>
       <c r="E73">
-        <v>2698.697</v>
+        <v>2739.504</v>
       </c>
       <c r="F73">
-        <v>2897.297</v>
+        <v>2938.104</v>
       </c>
       <c r="G73">
         <v>48.9</v>
@@ -7273,37 +7273,37 @@
         <v>186.6</v>
       </c>
       <c r="M73">
-        <v>683.1826325999999</v>
+        <v>692.8049232</v>
       </c>
       <c r="N73">
-        <v>-496.5826325999999</v>
+        <v>-506.2049231999999</v>
       </c>
       <c r="O73">
-        <v>-158.906442432</v>
+        <v>-161.985575424</v>
       </c>
       <c r="P73">
-        <v>-337.6761901679999</v>
+        <v>-344.2193477759999</v>
       </c>
       <c r="Q73">
-        <v>-291.4761901679999</v>
+        <v>-298.0193477759999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2590797169212004</v>
+        <v>0.2666968496683861</v>
       </c>
       <c r="T73">
-        <v>2.779749689390089</v>
+        <v>2.879026464011163</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.087402690218797</v>
+        <v>0.08618876396575814</v>
       </c>
       <c r="W73">
-        <v>0.2151904456464077</v>
+        <v>0.2154766894568742</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2731334069337407</v>
+        <v>0.2693398873929943</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2298183343160976</v>
+        <v>0.2317183343160976</v>
       </c>
       <c r="C74">
-        <v>-1455.851351325523</v>
+        <v>-1511.306557176223</v>
       </c>
       <c r="D74">
-        <v>1433.352648674477</v>
+        <v>1418.704442823777</v>
       </c>
       <c r="E74">
-        <v>2739.504</v>
+        <v>2780.311</v>
       </c>
       <c r="F74">
-        <v>2938.104</v>
+        <v>2978.911</v>
       </c>
       <c r="G74">
         <v>48.9</v>
@@ -7355,37 +7355,37 @@
         <v>186.6</v>
       </c>
       <c r="M74">
-        <v>692.8049232</v>
+        <v>702.4272137999999</v>
       </c>
       <c r="N74">
-        <v>-506.2049231999999</v>
+        <v>-515.8272137999999</v>
       </c>
       <c r="O74">
-        <v>-161.985575424</v>
+        <v>-165.064708416</v>
       </c>
       <c r="P74">
-        <v>-344.2193477759999</v>
+        <v>-350.7625053839999</v>
       </c>
       <c r="Q74">
-        <v>-298.0193477759999</v>
+        <v>-304.5625053839999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2666968496683861</v>
+        <v>0.2748782144709189</v>
       </c>
       <c r="T74">
-        <v>2.879026464011163</v>
+        <v>2.985657073789354</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08618876396575814</v>
+        <v>0.08500809596622723</v>
       </c>
       <c r="W74">
-        <v>0.2154766894568742</v>
+        <v>0.2157550909711636</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2693398873929943</v>
+        <v>0.2656502998944601</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2317183343160976</v>
+        <v>0.2336183343160975</v>
       </c>
       <c r="C75">
-        <v>-1511.306557176223</v>
+        <v>-1566.465395888777</v>
       </c>
       <c r="D75">
-        <v>1418.704442823777</v>
+        <v>1404.352604111223</v>
       </c>
       <c r="E75">
-        <v>2780.311</v>
+        <v>2821.118</v>
       </c>
       <c r="F75">
-        <v>2978.911</v>
+        <v>3019.718</v>
       </c>
       <c r="G75">
         <v>48.9</v>
@@ -7437,37 +7437,37 @@
         <v>186.6</v>
       </c>
       <c r="M75">
-        <v>702.4272137999999</v>
+        <v>712.0495044</v>
       </c>
       <c r="N75">
-        <v>-515.8272137999999</v>
+        <v>-525.4495044</v>
       </c>
       <c r="O75">
-        <v>-165.064708416</v>
+        <v>-168.143841408</v>
       </c>
       <c r="P75">
-        <v>-350.7625053839999</v>
+        <v>-357.305662992</v>
       </c>
       <c r="Q75">
-        <v>-304.5625053839999</v>
+        <v>-311.105662992</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2748782144709189</v>
+        <v>0.2836889150274927</v>
       </c>
       <c r="T75">
-        <v>2.985657073789354</v>
+        <v>3.100490038165868</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08500809596622723</v>
+        <v>0.08385933791262953</v>
       </c>
       <c r="W75">
-        <v>0.2157550909711636</v>
+        <v>0.2160259681202019</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2656502998944601</v>
+        <v>0.2620604309769674</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2336183343160975</v>
+        <v>0.2355183343160976</v>
       </c>
       <c r="C76">
-        <v>-1566.465395888777</v>
+        <v>-1621.33677167739</v>
       </c>
       <c r="D76">
-        <v>1404.352604111223</v>
+        <v>1390.28822832261</v>
       </c>
       <c r="E76">
-        <v>2821.118</v>
+        <v>2861.925</v>
       </c>
       <c r="F76">
-        <v>3019.718</v>
+        <v>3060.525</v>
       </c>
       <c r="G76">
         <v>48.9</v>
@@ -7519,37 +7519,37 @@
         <v>186.6</v>
       </c>
       <c r="M76">
-        <v>712.0495044</v>
+        <v>721.671795</v>
       </c>
       <c r="N76">
-        <v>-525.4495044</v>
+        <v>-535.071795</v>
       </c>
       <c r="O76">
-        <v>-168.143841408</v>
+        <v>-171.2229744</v>
       </c>
       <c r="P76">
-        <v>-357.305662992</v>
+        <v>-363.8488206</v>
       </c>
       <c r="Q76">
-        <v>-311.105662992</v>
+        <v>-317.6488205999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2836889150274927</v>
+        <v>0.2932044716285924</v>
       </c>
       <c r="T76">
-        <v>3.100490038165868</v>
+        <v>3.224509639692503</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08385933791262953</v>
+        <v>0.08274121340712781</v>
       </c>
       <c r="W76">
-        <v>0.2160259681202019</v>
+        <v>0.2162896218785993</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2620604309769674</v>
+        <v>0.2585662918972744</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2355183343160976</v>
+        <v>0.2374183343160976</v>
       </c>
       <c r="C77">
-        <v>-1621.33677167739</v>
+        <v>-1675.929235595761</v>
       </c>
       <c r="D77">
-        <v>1390.28822832261</v>
+        <v>1376.502764404238</v>
       </c>
       <c r="E77">
-        <v>2861.925</v>
+        <v>2902.732</v>
       </c>
       <c r="F77">
-        <v>3060.525</v>
+        <v>3101.332</v>
       </c>
       <c r="G77">
         <v>48.9</v>
@@ -7601,37 +7601,37 @@
         <v>186.6</v>
       </c>
       <c r="M77">
-        <v>721.671795</v>
+        <v>731.2940856</v>
       </c>
       <c r="N77">
-        <v>-535.071795</v>
+        <v>-544.6940856</v>
       </c>
       <c r="O77">
-        <v>-171.2229744</v>
+        <v>-174.302107392</v>
       </c>
       <c r="P77">
-        <v>-363.8488206</v>
+        <v>-370.391978208</v>
       </c>
       <c r="Q77">
-        <v>-317.6488205999999</v>
+        <v>-324.1919782079999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2932044716285924</v>
+        <v>0.3035129912797838</v>
       </c>
       <c r="T77">
-        <v>3.224509639692503</v>
+        <v>3.358864208013024</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08274121340712781</v>
+        <v>0.08165251323071823</v>
       </c>
       <c r="W77">
-        <v>0.2162896218785993</v>
+        <v>0.2165463373801967</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2585662918972744</v>
+        <v>0.2551641038459945</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2374183343160976</v>
+        <v>0.2393183343160976</v>
       </c>
       <c r="C78">
-        <v>-1675.929235595761</v>
+        <v>-1730.25100287407</v>
       </c>
       <c r="D78">
-        <v>1376.502764404238</v>
+        <v>1362.98799712593</v>
       </c>
       <c r="E78">
-        <v>2902.732</v>
+        <v>2943.539</v>
       </c>
       <c r="F78">
-        <v>3101.332</v>
+        <v>3142.139</v>
       </c>
       <c r="G78">
         <v>48.9</v>
@@ -7683,37 +7683,37 @@
         <v>186.6</v>
       </c>
       <c r="M78">
-        <v>731.2940856</v>
+        <v>740.9163762000001</v>
       </c>
       <c r="N78">
-        <v>-544.6940856</v>
+        <v>-554.3163762</v>
       </c>
       <c r="O78">
-        <v>-174.302107392</v>
+        <v>-177.381240384</v>
       </c>
       <c r="P78">
-        <v>-370.391978208</v>
+        <v>-376.935135816</v>
       </c>
       <c r="Q78">
-        <v>-324.1919782079999</v>
+        <v>-330.735135816</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3035129912797838</v>
+        <v>0.3147179039441222</v>
       </c>
       <c r="T78">
-        <v>3.358864208013024</v>
+        <v>3.50490178227446</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08165251323071823</v>
+        <v>0.08059209098096864</v>
       </c>
       <c r="W78">
-        <v>0.2165463373801967</v>
+        <v>0.2167963849466876</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2551641038459945</v>
+        <v>0.251850284315527</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2393183343160976</v>
+        <v>0.2412183343160976</v>
       </c>
       <c r="C79">
-        <v>-1730.25100287407</v>
+        <v>-1784.309969244586</v>
       </c>
       <c r="D79">
-        <v>1362.98799712593</v>
+        <v>1349.736030755413</v>
       </c>
       <c r="E79">
-        <v>2943.539</v>
+        <v>2984.346</v>
       </c>
       <c r="F79">
-        <v>3142.139</v>
+        <v>3182.946</v>
       </c>
       <c r="G79">
         <v>48.9</v>
@@ -7765,37 +7765,37 @@
         <v>186.6</v>
       </c>
       <c r="M79">
-        <v>740.9163762000001</v>
+        <v>750.5386668</v>
       </c>
       <c r="N79">
-        <v>-554.3163762</v>
+        <v>-563.9386668</v>
       </c>
       <c r="O79">
-        <v>-177.381240384</v>
+        <v>-180.460373376</v>
       </c>
       <c r="P79">
-        <v>-376.935135816</v>
+        <v>-383.478293424</v>
       </c>
       <c r="Q79">
-        <v>-330.735135816</v>
+        <v>-337.2782934239999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3147179039441222</v>
+        <v>0.3269414450324915</v>
       </c>
       <c r="T79">
-        <v>3.50490178227446</v>
+        <v>3.664215499650572</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08059209098096864</v>
+        <v>0.07955885904531522</v>
       </c>
       <c r="W79">
-        <v>0.2167963849466876</v>
+        <v>0.2170400210371147</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.251850284315527</v>
+        <v>0.2486214345166101</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2412183343160976</v>
+        <v>0.2431183343160976</v>
       </c>
       <c r="C80">
-        <v>-1784.309969244586</v>
+        <v>-1838.113726324073</v>
       </c>
       <c r="D80">
-        <v>1349.736030755413</v>
+        <v>1336.739273675927</v>
       </c>
       <c r="E80">
-        <v>2984.346</v>
+        <v>3025.153</v>
       </c>
       <c r="F80">
-        <v>3182.946</v>
+        <v>3223.753</v>
       </c>
       <c r="G80">
         <v>48.9</v>
@@ -7847,37 +7847,37 @@
         <v>186.6</v>
       </c>
       <c r="M80">
-        <v>750.5386668</v>
+        <v>760.1609574</v>
       </c>
       <c r="N80">
-        <v>-563.9386668</v>
+        <v>-573.5609574</v>
       </c>
       <c r="O80">
-        <v>-180.460373376</v>
+        <v>-183.539506368</v>
       </c>
       <c r="P80">
-        <v>-383.478293424</v>
+        <v>-390.021451032</v>
       </c>
       <c r="Q80">
-        <v>-337.2782934239999</v>
+        <v>-343.8214510319999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3269414450324915</v>
+        <v>0.3403291328911815</v>
       </c>
       <c r="T80">
-        <v>3.664215499650572</v>
+        <v>3.838701952014885</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07955885904531522</v>
+        <v>0.07855178488018463</v>
       </c>
       <c r="W80">
-        <v>0.2170400210371147</v>
+        <v>0.2172774891252525</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2486214345166101</v>
+        <v>0.245474327750577</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2431183343160976</v>
+        <v>0.2450183343160975</v>
       </c>
       <c r="C81">
-        <v>-1838.113726324073</v>
+        <v>-1891.669576115952</v>
       </c>
       <c r="D81">
-        <v>1336.739273675927</v>
+        <v>1323.990423884048</v>
       </c>
       <c r="E81">
-        <v>3025.153</v>
+        <v>3065.96</v>
       </c>
       <c r="F81">
-        <v>3223.753</v>
+        <v>3264.56</v>
       </c>
       <c r="G81">
         <v>48.9</v>
@@ -7929,37 +7929,37 @@
         <v>186.6</v>
       </c>
       <c r="M81">
-        <v>760.1609574</v>
+        <v>769.7832480000001</v>
       </c>
       <c r="N81">
-        <v>-573.5609574</v>
+        <v>-583.183248</v>
       </c>
       <c r="O81">
-        <v>-183.539506368</v>
+        <v>-186.61863936</v>
       </c>
       <c r="P81">
-        <v>-390.021451032</v>
+        <v>-396.56460864</v>
       </c>
       <c r="Q81">
-        <v>-343.8214510319999</v>
+        <v>-350.36460864</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3403291328911815</v>
+        <v>0.3550555895357406</v>
       </c>
       <c r="T81">
-        <v>3.838701952014885</v>
+        <v>4.030637049615629</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07855178488018463</v>
+        <v>0.07756988756918232</v>
       </c>
       <c r="W81">
-        <v>0.2172774891252525</v>
+        <v>0.2175090205111868</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.245474327750577</v>
+        <v>0.2424058986536948</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2450183343160975</v>
+        <v>0.2469183343160976</v>
       </c>
       <c r="C82">
-        <v>-1891.669576115952</v>
+        <v>-1944.984544690444</v>
       </c>
       <c r="D82">
-        <v>1323.990423884048</v>
+        <v>1311.482455309556</v>
       </c>
       <c r="E82">
-        <v>3065.96</v>
+        <v>3106.767</v>
       </c>
       <c r="F82">
-        <v>3264.56</v>
+        <v>3305.367</v>
       </c>
       <c r="G82">
         <v>48.9</v>
@@ -8011,37 +8011,37 @@
         <v>186.6</v>
       </c>
       <c r="M82">
-        <v>769.7832480000001</v>
+        <v>779.4055386000001</v>
       </c>
       <c r="N82">
-        <v>-583.183248</v>
+        <v>-592.8055386000001</v>
       </c>
       <c r="O82">
-        <v>-186.61863936</v>
+        <v>-189.697772352</v>
       </c>
       <c r="P82">
-        <v>-396.56460864</v>
+        <v>-403.1077662480001</v>
       </c>
       <c r="Q82">
-        <v>-350.36460864</v>
+        <v>-356.907766248</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3550555895357406</v>
+        <v>0.3713321995113059</v>
       </c>
       <c r="T82">
-        <v>4.030637049615629</v>
+        <v>4.242775841700663</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07756988756918232</v>
+        <v>0.07661223463622945</v>
       </c>
       <c r="W82">
-        <v>0.2175090205111868</v>
+        <v>0.2177348350727771</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2424058986536948</v>
+        <v>0.2394132332382171</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2469183343160976</v>
+        <v>0.2488183343160976</v>
       </c>
       <c r="C83">
-        <v>-1944.984544690444</v>
+        <v>-1998.065395096528</v>
       </c>
       <c r="D83">
-        <v>1311.482455309556</v>
+        <v>1299.208604903472</v>
       </c>
       <c r="E83">
-        <v>3106.767</v>
+        <v>3147.574</v>
       </c>
       <c r="F83">
-        <v>3305.367</v>
+        <v>3346.174</v>
       </c>
       <c r="G83">
         <v>48.9</v>
@@ -8093,37 +8093,37 @@
         <v>186.6</v>
       </c>
       <c r="M83">
-        <v>779.4055386000001</v>
+        <v>789.0278292</v>
       </c>
       <c r="N83">
-        <v>-592.8055386000001</v>
+        <v>-602.4278292</v>
       </c>
       <c r="O83">
-        <v>-189.697772352</v>
+        <v>-192.776905344</v>
       </c>
       <c r="P83">
-        <v>-403.1077662480001</v>
+        <v>-409.650923856</v>
       </c>
       <c r="Q83">
-        <v>-356.907766248</v>
+        <v>-363.450923856</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3713321995113059</v>
+        <v>0.3894173217063785</v>
       </c>
       <c r="T83">
-        <v>4.242775841700663</v>
+        <v>4.478485610684033</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07661223463622945</v>
+        <v>0.07567793909188519</v>
       </c>
       <c r="W83">
-        <v>0.2177348350727771</v>
+        <v>0.2179551419621335</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2394132332382171</v>
+        <v>0.2364935596621413</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2488183343160976</v>
+        <v>0.2507183343160976</v>
       </c>
       <c r="C84">
-        <v>-1998.065395096528</v>
+        <v>-2050.918639555595</v>
       </c>
       <c r="D84">
-        <v>1299.208604903472</v>
+        <v>1287.162360444405</v>
       </c>
       <c r="E84">
-        <v>3147.574</v>
+        <v>3188.381</v>
       </c>
       <c r="F84">
-        <v>3346.174</v>
+        <v>3386.981</v>
       </c>
       <c r="G84">
         <v>48.9</v>
@@ -8175,37 +8175,37 @@
         <v>186.6</v>
       </c>
       <c r="M84">
-        <v>789.0278292</v>
+        <v>798.6501198000001</v>
       </c>
       <c r="N84">
-        <v>-602.4278292</v>
+        <v>-612.0501198000001</v>
       </c>
       <c r="O84">
-        <v>-192.776905344</v>
+        <v>-195.856038336</v>
       </c>
       <c r="P84">
-        <v>-409.650923856</v>
+        <v>-416.1940814640001</v>
       </c>
       <c r="Q84">
-        <v>-363.450923856</v>
+        <v>-369.994081464</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3894173217063785</v>
+        <v>0.4096301053361655</v>
       </c>
       <c r="T84">
-        <v>4.478485610684033</v>
+        <v>4.74192594072427</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07567793909188519</v>
+        <v>0.07476615669318779</v>
       </c>
       <c r="W84">
-        <v>0.2179551419621335</v>
+        <v>0.2181701402517463</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2364935596621413</v>
+        <v>0.2336442396662118</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2507183343160976</v>
+        <v>0.2526183343160976</v>
       </c>
       <c r="C85">
-        <v>-2050.918639555595</v>
+        <v>-2103.550550982966</v>
       </c>
       <c r="D85">
-        <v>1287.162360444405</v>
+        <v>1275.337449017034</v>
       </c>
       <c r="E85">
-        <v>3188.381</v>
+        <v>3229.188</v>
       </c>
       <c r="F85">
-        <v>3386.981</v>
+        <v>3427.788</v>
       </c>
       <c r="G85">
         <v>48.9</v>
@@ -8257,37 +8257,37 @@
         <v>186.6</v>
       </c>
       <c r="M85">
-        <v>798.6501198000001</v>
+        <v>808.2724104</v>
       </c>
       <c r="N85">
-        <v>-612.0501198000001</v>
+        <v>-621.6724104</v>
       </c>
       <c r="O85">
-        <v>-195.856038336</v>
+        <v>-198.935171328</v>
       </c>
       <c r="P85">
-        <v>-416.1940814640001</v>
+        <v>-422.737239072</v>
       </c>
       <c r="Q85">
-        <v>-369.994081464</v>
+        <v>-376.5372390719999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4096301053361655</v>
+        <v>0.4323694869196759</v>
       </c>
       <c r="T85">
-        <v>4.74192594072427</v>
+        <v>5.038296312019539</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07476615669318779</v>
+        <v>0.07387608339922126</v>
       </c>
       <c r="W85">
-        <v>0.2181701402517463</v>
+        <v>0.2183800195344636</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2336442396662118</v>
+        <v>0.2308627606225665</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2526183343160976</v>
+        <v>0.2545183343160975</v>
       </c>
       <c r="C86">
-        <v>-2103.550550982966</v>
+        <v>-2155.967173880122</v>
       </c>
       <c r="D86">
-        <v>1275.337449017034</v>
+        <v>1263.727826119878</v>
       </c>
       <c r="E86">
-        <v>3229.188</v>
+        <v>3269.995</v>
       </c>
       <c r="F86">
-        <v>3427.788</v>
+        <v>3468.595</v>
       </c>
       <c r="G86">
         <v>48.9</v>
@@ -8339,37 +8339,37 @@
         <v>186.6</v>
       </c>
       <c r="M86">
-        <v>808.2724103999999</v>
+        <v>817.8947009999999</v>
       </c>
       <c r="N86">
-        <v>-621.6724103999999</v>
+        <v>-631.2947009999999</v>
       </c>
       <c r="O86">
-        <v>-198.935171328</v>
+        <v>-202.01430432</v>
       </c>
       <c r="P86">
-        <v>-422.7372390719999</v>
+        <v>-429.28039668</v>
       </c>
       <c r="Q86">
-        <v>-376.5372390719999</v>
+        <v>-383.0803966799999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4323694869196756</v>
+        <v>0.458140786047654</v>
       </c>
       <c r="T86">
-        <v>5.038296312019535</v>
+        <v>5.374182732820838</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07387608339922128</v>
+        <v>0.07300695300628926</v>
       </c>
       <c r="W86">
-        <v>0.2183800195344636</v>
+        <v>0.218584960481117</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2308627606225665</v>
+        <v>0.228146728144654</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2545183343160975</v>
+        <v>0.2564183343160976</v>
       </c>
       <c r="C87">
-        <v>-2155.967173880122</v>
+        <v>-2208.174334637371</v>
       </c>
       <c r="D87">
-        <v>1263.727826119878</v>
+        <v>1252.327665362628</v>
       </c>
       <c r="E87">
-        <v>3269.995</v>
+        <v>3310.802</v>
       </c>
       <c r="F87">
-        <v>3468.595</v>
+        <v>3509.402</v>
       </c>
       <c r="G87">
         <v>48.9</v>
@@ -8421,37 +8421,37 @@
         <v>186.6</v>
       </c>
       <c r="M87">
-        <v>817.8947009999999</v>
+        <v>827.5169916</v>
       </c>
       <c r="N87">
-        <v>-631.2947009999999</v>
+        <v>-640.9169916</v>
       </c>
       <c r="O87">
-        <v>-202.01430432</v>
+        <v>-205.093437312</v>
       </c>
       <c r="P87">
-        <v>-429.28039668</v>
+        <v>-435.823554288</v>
       </c>
       <c r="Q87">
-        <v>-383.0803966799999</v>
+        <v>-389.6235542879999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.458140786047654</v>
+        <v>0.4875936993367722</v>
       </c>
       <c r="T87">
-        <v>5.374182732820838</v>
+        <v>5.758052928022326</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07300695300628926</v>
+        <v>0.07215803494807659</v>
       </c>
       <c r="W87">
-        <v>0.218584960481117</v>
+        <v>0.2187851353592435</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.228146728144654</v>
+        <v>0.2254938592127393</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2564183343160976</v>
+        <v>0.2583183343160975</v>
       </c>
       <c r="C88">
-        <v>-2208.174334637371</v>
+        <v>-2260.177651283868</v>
       </c>
       <c r="D88">
-        <v>1252.327665362628</v>
+        <v>1241.131348716132</v>
       </c>
       <c r="E88">
-        <v>3310.802</v>
+        <v>3351.609</v>
       </c>
       <c r="F88">
-        <v>3509.402</v>
+        <v>3550.209</v>
       </c>
       <c r="G88">
         <v>48.9</v>
@@ -8503,37 +8503,37 @@
         <v>186.6</v>
       </c>
       <c r="M88">
-        <v>827.5169916</v>
+        <v>837.1392822</v>
       </c>
       <c r="N88">
-        <v>-640.9169916</v>
+        <v>-650.5392822</v>
       </c>
       <c r="O88">
-        <v>-205.093437312</v>
+        <v>-208.172570304</v>
       </c>
       <c r="P88">
-        <v>-435.823554288</v>
+        <v>-442.366711896</v>
       </c>
       <c r="Q88">
-        <v>-389.6235542879999</v>
+        <v>-396.1667118959999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4875936993367722</v>
+        <v>0.5215778300549854</v>
       </c>
       <c r="T88">
-        <v>5.758052928022326</v>
+        <v>6.200980076331736</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07215803494807659</v>
+        <v>0.07132863224752398</v>
       </c>
       <c r="W88">
-        <v>0.2187851353592435</v>
+        <v>0.2189807085160339</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2254938592127393</v>
+        <v>0.2229019757735125</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2583183343160975</v>
+        <v>0.2602183343160975</v>
       </c>
       <c r="C89">
-        <v>-2260.177651283868</v>
+        <v>-2311.982542719235</v>
       </c>
       <c r="D89">
-        <v>1241.131348716132</v>
+        <v>1230.133457280765</v>
       </c>
       <c r="E89">
-        <v>3351.609</v>
+        <v>3392.416</v>
       </c>
       <c r="F89">
-        <v>3550.209</v>
+        <v>3591.016</v>
       </c>
       <c r="G89">
         <v>48.9</v>
@@ -8585,37 +8585,37 @@
         <v>186.6</v>
       </c>
       <c r="M89">
-        <v>837.1392822</v>
+        <v>846.7615728000001</v>
       </c>
       <c r="N89">
-        <v>-650.5392822</v>
+        <v>-660.1615728</v>
       </c>
       <c r="O89">
-        <v>-208.172570304</v>
+        <v>-211.251703296</v>
       </c>
       <c r="P89">
-        <v>-442.366711896</v>
+        <v>-448.909869504</v>
       </c>
       <c r="Q89">
-        <v>-396.1667118959999</v>
+        <v>-402.709869504</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5215778300549854</v>
+        <v>0.5612259825595676</v>
       </c>
       <c r="T89">
-        <v>6.200980076331736</v>
+        <v>6.717728416026048</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07132863224752398</v>
+        <v>0.07051807960834756</v>
       </c>
       <c r="W89">
-        <v>0.2189807085160339</v>
+        <v>0.2191718368283516</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2229019757735125</v>
+        <v>0.2203689987760862</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2602183343160975</v>
+        <v>0.2621183343160975</v>
       </c>
       <c r="C90">
-        <v>-2311.982542719235</v>
+        <v>-2363.594237458693</v>
       </c>
       <c r="D90">
-        <v>1230.133457280765</v>
+        <v>1219.328762541307</v>
       </c>
       <c r="E90">
-        <v>3392.416</v>
+        <v>3433.223</v>
       </c>
       <c r="F90">
-        <v>3591.016</v>
+        <v>3631.823</v>
       </c>
       <c r="G90">
         <v>48.9</v>
@@ -8667,37 +8667,37 @@
         <v>186.6</v>
       </c>
       <c r="M90">
-        <v>846.7615728000001</v>
+        <v>856.3838634</v>
       </c>
       <c r="N90">
-        <v>-660.1615728</v>
+        <v>-669.7838634</v>
       </c>
       <c r="O90">
-        <v>-211.251703296</v>
+        <v>-214.330836288</v>
       </c>
       <c r="P90">
-        <v>-448.909869504</v>
+        <v>-455.453027112</v>
       </c>
       <c r="Q90">
-        <v>-402.709869504</v>
+        <v>-409.2530271119999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5612259825595676</v>
+        <v>0.6080828900649828</v>
       </c>
       <c r="T90">
-        <v>6.717728416026048</v>
+        <v>7.328430999301144</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07051807960834756</v>
+        <v>0.06972574163522008</v>
       </c>
       <c r="W90">
-        <v>0.2191718368283516</v>
+        <v>0.2193586701224151</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2203689987760862</v>
+        <v>0.2178929426100628</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2621183343160975</v>
+        <v>0.2640183343160976</v>
       </c>
       <c r="C91">
-        <v>-2363.594237458693</v>
+        <v>-2415.017781921326</v>
       </c>
       <c r="D91">
-        <v>1219.328762541307</v>
+        <v>1208.712218078674</v>
       </c>
       <c r="E91">
-        <v>3433.223</v>
+        <v>3474.03</v>
       </c>
       <c r="F91">
-        <v>3631.823</v>
+        <v>3672.63</v>
       </c>
       <c r="G91">
         <v>48.9</v>
@@ -8749,37 +8749,37 @@
         <v>186.6</v>
       </c>
       <c r="M91">
-        <v>856.3838634</v>
+        <v>866.006154</v>
       </c>
       <c r="N91">
-        <v>-669.7838634</v>
+        <v>-679.406154</v>
       </c>
       <c r="O91">
-        <v>-214.330836288</v>
+        <v>-217.40996928</v>
       </c>
       <c r="P91">
-        <v>-455.453027112</v>
+        <v>-461.99618472</v>
       </c>
       <c r="Q91">
-        <v>-409.2530271119999</v>
+        <v>-415.7961847199999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6080828900649828</v>
+        <v>0.6643111790714812</v>
       </c>
       <c r="T91">
-        <v>7.328430999301144</v>
+        <v>8.061274099231259</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06972574163522008</v>
+        <v>0.06895101117260652</v>
       </c>
       <c r="W91">
-        <v>0.2193586701224151</v>
+        <v>0.2195413515654994</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2178929426100628</v>
+        <v>0.2154719099143954</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2640183343160976</v>
+        <v>0.2659183343160976</v>
       </c>
       <c r="C92">
-        <v>-2415.017781921326</v>
+        <v>-2466.258048289095</v>
       </c>
       <c r="D92">
-        <v>1208.712218078674</v>
+        <v>1198.278951710905</v>
       </c>
       <c r="E92">
-        <v>3474.03</v>
+        <v>3514.837</v>
       </c>
       <c r="F92">
-        <v>3672.63</v>
+        <v>3713.437</v>
       </c>
       <c r="G92">
         <v>48.9</v>
@@ -8831,37 +8831,37 @@
         <v>186.6</v>
       </c>
       <c r="M92">
-        <v>866.006154</v>
+        <v>875.6284446</v>
       </c>
       <c r="N92">
-        <v>-679.406154</v>
+        <v>-689.0284445999999</v>
       </c>
       <c r="O92">
-        <v>-217.40996928</v>
+        <v>-220.489102272</v>
       </c>
       <c r="P92">
-        <v>-461.99618472</v>
+        <v>-468.539342328</v>
       </c>
       <c r="Q92">
-        <v>-415.7961847199999</v>
+        <v>-422.3393423279999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6643111790714812</v>
+        <v>0.7330346434127569</v>
       </c>
       <c r="T92">
-        <v>8.061274099231259</v>
+        <v>8.956971221368066</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06895101117260652</v>
+        <v>0.06819330775312732</v>
       </c>
       <c r="W92">
-        <v>0.2195413515654994</v>
+        <v>0.2197200180318126</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2154719099143954</v>
+        <v>0.2131040867285229</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2659183343160976</v>
+        <v>0.2678183343160975</v>
       </c>
       <c r="C93">
-        <v>-2466.258048289095</v>
+        <v>-2517.319741962317</v>
       </c>
       <c r="D93">
-        <v>1198.278951710905</v>
+        <v>1188.024258037682</v>
       </c>
       <c r="E93">
-        <v>3514.837</v>
+        <v>3555.644</v>
       </c>
       <c r="F93">
-        <v>3713.437</v>
+        <v>3754.244</v>
       </c>
       <c r="G93">
         <v>48.9</v>
@@ -8913,37 +8913,37 @@
         <v>186.6</v>
       </c>
       <c r="M93">
-        <v>875.6284446</v>
+        <v>885.2507352000001</v>
       </c>
       <c r="N93">
-        <v>-689.0284445999999</v>
+        <v>-698.6507352000001</v>
       </c>
       <c r="O93">
-        <v>-220.489102272</v>
+        <v>-223.568235264</v>
       </c>
       <c r="P93">
-        <v>-468.539342328</v>
+        <v>-475.0824999360001</v>
       </c>
       <c r="Q93">
-        <v>-422.3393423279999</v>
+        <v>-428.882499936</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7330346434127569</v>
+        <v>0.8189389738393517</v>
       </c>
       <c r="T93">
-        <v>8.956971221368066</v>
+        <v>10.07659262403908</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06819330775312732</v>
+        <v>0.06745207614711507</v>
       </c>
       <c r="W93">
-        <v>0.2197200180318126</v>
+        <v>0.2198948004445103</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2131040867285229</v>
+        <v>0.2107877379597346</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2678183343160975</v>
+        <v>0.2697183343160976</v>
       </c>
       <c r="C94">
-        <v>-2517.319741962317</v>
+        <v>-2568.207408635575</v>
       </c>
       <c r="D94">
-        <v>1188.024258037682</v>
+        <v>1177.943591364424</v>
       </c>
       <c r="E94">
-        <v>3555.644</v>
+        <v>3596.451</v>
       </c>
       <c r="F94">
-        <v>3754.244</v>
+        <v>3795.051</v>
       </c>
       <c r="G94">
         <v>48.9</v>
@@ -8995,37 +8995,37 @@
         <v>186.6</v>
       </c>
       <c r="M94">
-        <v>885.2507352000001</v>
+        <v>894.8730258000001</v>
       </c>
       <c r="N94">
-        <v>-698.6507352000001</v>
+        <v>-708.2730258</v>
       </c>
       <c r="O94">
-        <v>-223.568235264</v>
+        <v>-226.647368256</v>
       </c>
       <c r="P94">
-        <v>-475.0824999360001</v>
+        <v>-481.625657544</v>
       </c>
       <c r="Q94">
-        <v>-428.882499936</v>
+        <v>-435.4256575439999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8189389738393517</v>
+        <v>0.929387398673545</v>
       </c>
       <c r="T94">
-        <v>10.07659262403908</v>
+        <v>11.51610585604466</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06745207614711507</v>
+        <v>0.06672678500574823</v>
       </c>
       <c r="W94">
-        <v>0.2198948004445103</v>
+        <v>0.2200658240956446</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2107877379597346</v>
+        <v>0.2085212031429633</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2697183343160976</v>
+        <v>0.2716183343160976</v>
       </c>
       <c r="C95">
-        <v>-2568.207408635575</v>
+        <v>-2618.925441016408</v>
       </c>
       <c r="D95">
-        <v>1177.943591364424</v>
+        <v>1168.032558983592</v>
       </c>
       <c r="E95">
-        <v>3596.451</v>
+        <v>3637.258</v>
       </c>
       <c r="F95">
-        <v>3795.051</v>
+        <v>3835.858</v>
       </c>
       <c r="G95">
         <v>48.9</v>
@@ -9077,37 +9077,37 @@
         <v>186.6</v>
       </c>
       <c r="M95">
-        <v>894.8730258000001</v>
+        <v>904.4953164000001</v>
       </c>
       <c r="N95">
-        <v>-708.2730258</v>
+        <v>-717.8953164000001</v>
       </c>
       <c r="O95">
-        <v>-226.647368256</v>
+        <v>-229.726501248</v>
       </c>
       <c r="P95">
-        <v>-481.625657544</v>
+        <v>-488.168815152</v>
       </c>
       <c r="Q95">
-        <v>-435.4256575439999</v>
+        <v>-441.968815152</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.929387398673545</v>
+        <v>1.076651965119136</v>
       </c>
       <c r="T95">
-        <v>11.51610585604466</v>
+        <v>13.43545683205211</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06672678500574823</v>
+        <v>0.06601692559079346</v>
       </c>
       <c r="W95">
-        <v>0.2200658240956446</v>
+        <v>0.2202332089456909</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2085212031429633</v>
+        <v>0.2063028924712296</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2716183343160976</v>
+        <v>0.2735183343160976</v>
       </c>
       <c r="C96">
-        <v>-2618.925441016408</v>
+        <v>-2669.478085207657</v>
       </c>
       <c r="D96">
-        <v>1168.032558983592</v>
+        <v>1158.286914792342</v>
       </c>
       <c r="E96">
-        <v>3637.258</v>
+        <v>3678.065</v>
       </c>
       <c r="F96">
-        <v>3835.858</v>
+        <v>3876.665</v>
       </c>
       <c r="G96">
         <v>48.9</v>
@@ -9159,37 +9159,37 @@
         <v>186.6</v>
       </c>
       <c r="M96">
-        <v>904.4953164000001</v>
+        <v>914.117607</v>
       </c>
       <c r="N96">
-        <v>-717.8953164000001</v>
+        <v>-727.517607</v>
       </c>
       <c r="O96">
-        <v>-229.726501248</v>
+        <v>-232.80563424</v>
       </c>
       <c r="P96">
-        <v>-488.168815152</v>
+        <v>-494.71197276</v>
       </c>
       <c r="Q96">
-        <v>-441.968815152</v>
+        <v>-448.5119727599999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.076651965119136</v>
+        <v>1.282822358142964</v>
       </c>
       <c r="T96">
-        <v>13.43545683205211</v>
+        <v>16.12254819846254</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06601692559079346</v>
+        <v>0.0653220105845746</v>
       </c>
       <c r="W96">
-        <v>0.2202332089456909</v>
+        <v>0.2203970699041573</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2063028924712296</v>
+        <v>0.2041312830767956</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2735183343160976</v>
+        <v>0.2754183343160976</v>
       </c>
       <c r="C97">
-        <v>-2669.478085207657</v>
+        <v>-2719.869446772949</v>
       </c>
       <c r="D97">
-        <v>1158.286914792342</v>
+        <v>1148.702553227051</v>
       </c>
       <c r="E97">
-        <v>3678.065</v>
+        <v>3718.872</v>
       </c>
       <c r="F97">
-        <v>3876.665</v>
+        <v>3917.472</v>
       </c>
       <c r="G97">
         <v>48.9</v>
@@ -9241,37 +9241,37 @@
         <v>186.6</v>
       </c>
       <c r="M97">
-        <v>914.117607</v>
+        <v>923.7398976000001</v>
       </c>
       <c r="N97">
-        <v>-727.517607</v>
+        <v>-737.1398976</v>
       </c>
       <c r="O97">
-        <v>-232.80563424</v>
+        <v>-235.884767232</v>
       </c>
       <c r="P97">
-        <v>-494.71197276</v>
+        <v>-501.255130368</v>
       </c>
       <c r="Q97">
-        <v>-448.5119727599999</v>
+        <v>-455.0551303679999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.282822358142964</v>
+        <v>1.592077947678706</v>
       </c>
       <c r="T97">
-        <v>16.12254819846254</v>
+        <v>20.15318524807818</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0653220105845746</v>
+        <v>0.06464157297431861</v>
       </c>
       <c r="W97">
-        <v>0.2203970699041573</v>
+        <v>0.2205575170926557</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2041312830767956</v>
+        <v>0.2020049155447456</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2754183343160975</v>
+        <v>0.2773183343160975</v>
       </c>
       <c r="C98">
-        <v>-2719.869446772948</v>
+        <v>-2770.103496503496</v>
       </c>
       <c r="D98">
-        <v>1148.702553227052</v>
+        <v>1139.275503496504</v>
       </c>
       <c r="E98">
-        <v>3718.872</v>
+        <v>3759.679</v>
       </c>
       <c r="F98">
-        <v>3917.472</v>
+        <v>3958.279</v>
       </c>
       <c r="G98">
         <v>48.9</v>
@@ -9323,37 +9323,37 @@
         <v>186.6</v>
       </c>
       <c r="M98">
-        <v>923.7398975999999</v>
+        <v>933.3621881999999</v>
       </c>
       <c r="N98">
-        <v>-737.1398975999999</v>
+        <v>-746.7621881999999</v>
       </c>
       <c r="O98">
-        <v>-235.884767232</v>
+        <v>-238.963900224</v>
       </c>
       <c r="P98">
-        <v>-501.255130368</v>
+        <v>-507.7982879759999</v>
       </c>
       <c r="Q98">
-        <v>-455.0551303679999</v>
+        <v>-461.5982879759998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.592077947678701</v>
+        <v>2.107503930238269</v>
       </c>
       <c r="T98">
-        <v>20.15318524807812</v>
+        <v>26.87091366410417</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06464157297431862</v>
+        <v>0.06397516500551122</v>
       </c>
       <c r="W98">
-        <v>0.2205575170926557</v>
+        <v>0.2207146560917005</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2020049155447456</v>
+        <v>0.1999223906422225</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2773183343160975</v>
+        <v>0.2792183343160975</v>
       </c>
       <c r="C99">
-        <v>-2770.103496503496</v>
+        <v>-2820.18407590327</v>
       </c>
       <c r="D99">
-        <v>1139.275503496504</v>
+        <v>1130.001924096729</v>
       </c>
       <c r="E99">
-        <v>3759.679</v>
+        <v>3800.486</v>
       </c>
       <c r="F99">
-        <v>3958.279</v>
+        <v>3999.086</v>
       </c>
       <c r="G99">
         <v>48.9</v>
@@ -9405,37 +9405,37 @@
         <v>186.6</v>
       </c>
       <c r="M99">
-        <v>933.3621881999999</v>
+        <v>942.9844788</v>
       </c>
       <c r="N99">
-        <v>-746.7621881999999</v>
+        <v>-756.3844788</v>
       </c>
       <c r="O99">
-        <v>-238.963900224</v>
+        <v>-242.043033216</v>
       </c>
       <c r="P99">
-        <v>-507.7982879759999</v>
+        <v>-514.341445584</v>
       </c>
       <c r="Q99">
-        <v>-461.5982879759998</v>
+        <v>-468.1414455839999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.107503930238269</v>
+        <v>3.138355895357402</v>
       </c>
       <c r="T99">
-        <v>26.87091366410417</v>
+        <v>40.30637049615625</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06397516500551122</v>
+        <v>0.06332235719933252</v>
       </c>
       <c r="W99">
-        <v>0.2207146560917005</v>
+        <v>0.2208685881723974</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1999223906422225</v>
+        <v>0.1978823662479141</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2792183343160975</v>
+        <v>0.2811183343160976</v>
       </c>
       <c r="C100">
-        <v>-2820.18407590327</v>
+        <v>-2870.114902408432</v>
       </c>
       <c r="D100">
-        <v>1130.001924096729</v>
+        <v>1120.878097591568</v>
       </c>
       <c r="E100">
-        <v>3800.486</v>
+        <v>3841.293</v>
       </c>
       <c r="F100">
-        <v>3999.086</v>
+        <v>4039.893</v>
       </c>
       <c r="G100">
         <v>48.9</v>
@@ -9487,37 +9487,37 @@
         <v>186.6</v>
       </c>
       <c r="M100">
-        <v>942.9844788</v>
+        <v>952.6067694</v>
       </c>
       <c r="N100">
-        <v>-756.3844788</v>
+        <v>-766.0067693999999</v>
       </c>
       <c r="O100">
-        <v>-242.043033216</v>
+        <v>-245.122166208</v>
       </c>
       <c r="P100">
-        <v>-514.341445584</v>
+        <v>-520.884603192</v>
       </c>
       <c r="Q100">
-        <v>-468.1414455839999</v>
+        <v>-474.6846031919999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.138355895357402</v>
+        <v>6.230911790714805</v>
       </c>
       <c r="T100">
-        <v>40.30637049615625</v>
+        <v>80.61274099231251</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06332235719933252</v>
+        <v>0.06268273742964228</v>
       </c>
       <c r="W100">
-        <v>0.2208685881723974</v>
+        <v>0.2210194105140904</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1978823662479141</v>
+        <v>0.1958835544676322</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2811183343160976</v>
-      </c>
-      <c r="C101">
-        <v>-2870.114902408432</v>
-      </c>
-      <c r="D101">
-        <v>1120.878097591568</v>
-      </c>
-      <c r="E101">
-        <v>3841.293</v>
-      </c>
-      <c r="F101">
-        <v>4039.893</v>
-      </c>
-      <c r="G101">
-        <v>48.9</v>
-      </c>
-      <c r="H101">
-        <v>3882.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>232.8</v>
-      </c>
-      <c r="K101">
-        <v>46.20000000000002</v>
-      </c>
-      <c r="L101">
-        <v>186.6</v>
-      </c>
-      <c r="M101">
-        <v>952.6067694</v>
-      </c>
-      <c r="N101">
-        <v>-766.0067693999999</v>
-      </c>
-      <c r="O101">
-        <v>-245.122166208</v>
-      </c>
-      <c r="P101">
-        <v>-520.884603192</v>
-      </c>
-      <c r="Q101">
-        <v>-474.6846031919999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.230911790714805</v>
-      </c>
-      <c r="T101">
-        <v>80.61274099231251</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06268273742964228</v>
-      </c>
-      <c r="W101">
-        <v>0.2210194105140904</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1958835544676322</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
